--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-17  -  generated 2026-09-17 15:38 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-18  -  generated 2026-09-18 15:07 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>80.73</v>
+        <v>76.22</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>155.815</v>
+        <v>157.154</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.075</v>
+        <v>4.047</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6951</v>
+        <v>6.6895</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>311.3</v>
+        <v>312</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4398.2998</v>
+        <v>4396.8999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.6545</v>
+        <v>6.663</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>100.59</v>
+        <v>97.02</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.86</v>
+        <v>15.29</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>80.73</v>
+        <v>76.22</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="G63" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8410,17 +8410,17 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8494,17 +8494,17 @@
       </c>
       <c r="E76" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9502,17 +9502,17 @@
       </c>
       <c r="E100" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F100" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G100" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="E165" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F165" s="9" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="E172" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F172" s="9" t="inlineStr">
@@ -12536,7 +12536,7 @@
       </c>
       <c r="G172" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12820,17 +12820,17 @@
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17230,17 +17230,17 @@
       </c>
       <c r="E284" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F284" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G284" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17314,17 +17314,17 @@
       </c>
       <c r="E286" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F286" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G286" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17366,7 +17366,7 @@
       </c>
       <c r="G287" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="E373" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F373" s="9" t="inlineStr">
@@ -20978,7 +20978,7 @@
       </c>
       <c r="G373" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21062,7 +21062,7 @@
       </c>
       <c r="G375" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21094,17 +21094,17 @@
       </c>
       <c r="E376" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F376" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G376" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="G380" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="G388" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="G391" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="G412" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25546,17 +25546,17 @@
       </c>
       <c r="E482" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F482" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G482" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="E485" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F485" s="9" t="inlineStr">
@@ -25682,7 +25682,7 @@
       </c>
       <c r="G485" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25966,17 +25966,17 @@
       </c>
       <c r="E492" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F492" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G492" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="G493" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26134,17 +26134,17 @@
       </c>
       <c r="E496" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F496" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28454,7 +28454,7 @@
       </c>
       <c r="G551" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29956,17 +29956,17 @@
       </c>
       <c r="E587" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F587" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G587" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="G598" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30554,7 +30554,7 @@
       </c>
       <c r="G601" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34292,7 +34292,7 @@
       </c>
       <c r="G690" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34628,7 +34628,7 @@
       </c>
       <c r="G698" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34786,17 +34786,17 @@
       </c>
       <c r="E702" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F702" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G702" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="G703" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="G761" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38156,7 +38156,7 @@
       </c>
       <c r="G782" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38702,7 +38702,7 @@
       </c>
       <c r="G795" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="G808" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39280,17 +39280,17 @@
       </c>
       <c r="E809" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F809" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G809" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="G811" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43312,17 +43312,17 @@
       </c>
       <c r="E905" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F905" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G905" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43564,17 +43564,17 @@
       </c>
       <c r="E911" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F911" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G911" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43658,7 +43658,7 @@
       </c>
       <c r="G913" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43690,17 +43690,17 @@
       </c>
       <c r="E914" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F914" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G914" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43774,7 +43774,7 @@
       </c>
       <c r="E916" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F916" s="9" t="inlineStr">
@@ -43784,7 +43784,7 @@
       </c>
       <c r="G916" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47302,7 +47302,7 @@
       </c>
       <c r="E1000" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F1000" s="9" t="inlineStr">
@@ -47312,7 +47312,7 @@
       </c>
       <c r="G1000" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,34 +47455,38 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-09-17) ---</t>
+          <t>--- Daily narrative (2026-09-18) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-09-17</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk remains High, with undersea cable vulnerabilities edging down but financial leverage and supply-chain choke points dominating the landscape.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** System-wide macro risk remains High, anchored by opaque credit expansion and geopolitical supply-chain exposure.</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**CHANGES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**No intraday level changes recorded.**</t>
+          <t>• **Sea lanes &amp; undersea cables** (High, 8→7): Red Sea undersea cable cut confirmed; repair timeline extends months. Risk persists despite marginal score reduction—physical infrastructure remains exposed to regional disruption.</t>
         </is>
       </c>
     </row>
@@ -47492,67 +47496,31 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**Elevated or Higher Stories (standing risks):**</t>
+          <t>**ELEVATED OR HIGHER AT EOD**</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr"/>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Three stories at High: Japan fiscal/JGB/carry trade (7), private credit's opaque expansion (8), critical minerals as weapon (7). Nine Elevated stories span Treasury basis trades, dev-world debt, China deflation, AI financing, eurozone fragility, consumer debt, grid bottlenecks, water pricing, and lithography chokepoints.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>• **Private credit's opaque expansion** (High) – Unregulated leverage and valuation opacity in non-bank lending pose direct contagion risk to funding markets if repricing occurs.</t>
-        </is>
-      </c>
+      <c r="A22" s="12" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**KEY WATCH**</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (High) – Persistent chokepoint vulnerability in critical infrastructure creates tail risk to trade and digital connectivity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High) – Structural imbalances in Japan's debt servicing and yen carry unwind potential remain destabilizing vectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr">
-        <is>
-          <t>• **Critical minerals as a weapon** (High) – Geopolitical weaponization of mineral supply chains continues to threaten industrial supply resilience.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>• **Treasury basis trade, developing-world debt, China spillover, AI financing, and infrastructure bottlenecks** all remain **Elevated**, with material tail risk in credit stress and supply shocks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="12" t="inlineStr">
-        <is>
-          <t>**Watch closest:** Private credit opacity—largest unmonitored leverage pool in the system.</t>
+          <t>Private credit's opaque expansion at level 8 (High) poses the greatest systemic risk given its scale, opacity, and interconnection to leveraged finance.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-18  -  generated 2026-09-18 15:07 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-21  -  generated 2026-09-21 17:14 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>76.22</v>
+        <v>80.64</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.154</v>
+        <v>157.401</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.68</v>
+        <v>2.61</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6895</v>
+        <v>6.6835</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>312</v>
+        <v>311.1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="D28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4396.8999</v>
+        <v>4380.6001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.663</v>
+        <v>6.7595</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>97.02</v>
+        <v>91.55</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.29</v>
+        <v>15.03</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>76.22</v>
+        <v>80.64</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="G39" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F53" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G53" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7612,17 +7612,17 @@
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F55" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8620,17 +8620,17 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="E144" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F144" s="9" t="inlineStr">
@@ -11360,7 +11360,7 @@
       </c>
       <c r="G144" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="E151" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F151" s="9" t="inlineStr">
@@ -11654,7 +11654,7 @@
       </c>
       <c r="G151" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11938,17 +11938,17 @@
       </c>
       <c r="E158" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F158" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G158" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15676,7 +15676,7 @@
       </c>
       <c r="E247" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F247" s="9" t="inlineStr">
@@ -15686,7 +15686,7 @@
       </c>
       <c r="G247" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15770,7 +15770,7 @@
       </c>
       <c r="G249" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16348,17 +16348,17 @@
       </c>
       <c r="E263" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F263" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G263" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16432,17 +16432,17 @@
       </c>
       <c r="E265" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F265" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G265" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16484,7 +16484,7 @@
       </c>
       <c r="G266" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20086,7 +20086,7 @@
       </c>
       <c r="E352" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F352" s="9" t="inlineStr">
@@ -20096,7 +20096,7 @@
       </c>
       <c r="G352" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20180,7 +20180,7 @@
       </c>
       <c r="G354" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20212,17 +20212,17 @@
       </c>
       <c r="E355" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F355" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G355" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="E359" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F359" s="9" t="inlineStr">
@@ -20390,7 +20390,7 @@
       </c>
       <c r="G359" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="G367" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="G370" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21734,7 +21734,7 @@
       </c>
       <c r="G391" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24664,17 +24664,17 @@
       </c>
       <c r="E461" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F461" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G461" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24790,7 +24790,7 @@
       </c>
       <c r="E464" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F464" s="9" t="inlineStr">
@@ -24800,7 +24800,7 @@
       </c>
       <c r="G464" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25084,17 +25084,17 @@
       </c>
       <c r="E471" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F471" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G471" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="G472" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25252,17 +25252,17 @@
       </c>
       <c r="E475" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F475" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G475" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="G530" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29074,17 +29074,17 @@
       </c>
       <c r="E566" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F566" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G566" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29546,7 +29546,7 @@
       </c>
       <c r="G577" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29672,7 +29672,7 @@
       </c>
       <c r="G580" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33410,7 +33410,7 @@
       </c>
       <c r="G669" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="G677" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33904,17 +33904,17 @@
       </c>
       <c r="E681" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F681" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G681" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33956,7 +33956,7 @@
       </c>
       <c r="G682" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="G740" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37274,7 +37274,7 @@
       </c>
       <c r="G761" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37820,7 +37820,7 @@
       </c>
       <c r="G774" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38366,7 +38366,7 @@
       </c>
       <c r="G787" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38398,17 +38398,17 @@
       </c>
       <c r="E788" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F788" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G788" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38492,7 +38492,7 @@
       </c>
       <c r="G790" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42430,17 +42430,17 @@
       </c>
       <c r="E884" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F884" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G884" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42682,17 +42682,17 @@
       </c>
       <c r="E890" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F890" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G890" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42776,7 +42776,7 @@
       </c>
       <c r="G892" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42808,17 +42808,17 @@
       </c>
       <c r="E893" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F893" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G893" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42892,7 +42892,7 @@
       </c>
       <c r="E895" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F895" s="9" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="G895" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46420,7 +46420,7 @@
       </c>
       <c r="E979" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F979" s="9" t="inlineStr">
@@ -46430,7 +46430,7 @@
       </c>
       <c r="G979" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46840,17 +46840,17 @@
       </c>
       <c r="E989" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F989" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G989" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,21 +47455,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-09-18) ---</t>
+          <t>--- Daily narrative (2026-09-21) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>As of 2026-09-21: overall risk 6.7/10 (High) (Set 1 5.8/10, Set 2 5.0/10, Set 3 4.5/10, Set 4 6.5/10, Set 5 5.2/10).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains High, with undersea cable vulnerabilities edging down but financial leverage and supply-chain choke points dominating the landscape.</t>
+          <t>- CRE maturity wall / regional banks: 4 -&gt; 5/10 (Elevated), up. Driver: CMBS office delinquency rate (%) now band 1; Regional-bank CRE stress (0 calm / 1 isolated / 2 cluster) now band 1.</t>
         </is>
       </c>
     </row>
@@ -47479,48 +47479,7 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**CHANGES**</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>• **Sea lanes &amp; undersea cables** (High, 8→7): Red Sea undersea cable cut confirmed; repair timeline extends months. Risk persists despite marginal score reduction—physical infrastructure remains exposed to regional disruption.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**ELEVATED OR HIGHER AT EOD**</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Three stories at High: Japan fiscal/JGB/carry trade (7), private credit's opaque expansion (8), critical minerals as weapon (7). Nine Elevated stories span Treasury basis trades, dev-world debt, China deflation, AI financing, eurozone fragility, consumer debt, grid bottlenecks, water pricing, and lithography chokepoints.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**KEY WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion at level 8 (High) poses the greatest systemic risk given its scale, opacity, and interconnection to leveraged finance.</t>
+          <t>(AI narrative unavailable: HTTP Error 400: Bad Request)</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-21  -  generated 2026-09-21 17:14 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-22  -  generated 2026-09-22 06:18 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>80.64</v>
+        <v>81.2</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.401</v>
+        <v>157.614</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         </is>
       </c>
       <c r="D11" s="7" t="n">
-        <v>118.2126</v>
+        <v>119.5133</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.61</v>
+        <v>2.68</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6835</v>
+        <v>6.6964</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>311.1</v>
+        <v>312</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         </is>
       </c>
       <c r="D32" s="7" t="n">
-        <v>5.67</v>
+        <v>6.13</v>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4380.6001</v>
+        <v>4358.2998</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.7595</v>
+        <v>6.818</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="D59" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>91.55</v>
+        <v>93.58</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.03</v>
+        <v>14.87</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>80.64</v>
+        <v>81.2</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="D64" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5974,17 +5974,17 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F18" s="9" t="inlineStr">
@@ -6068,7 +6068,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G21" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6646,17 +6646,17 @@
       </c>
       <c r="E32" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F32" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G32" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6730,17 +6730,17 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7738,17 +7738,17 @@
       </c>
       <c r="E58" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F58" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10468,7 +10468,7 @@
       </c>
       <c r="E123" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F123" s="9" t="inlineStr">
@@ -10478,7 +10478,7 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="E130" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F130" s="9" t="inlineStr">
@@ -10772,7 +10772,7 @@
       </c>
       <c r="G130" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11056,17 +11056,17 @@
       </c>
       <c r="E137" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F137" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14794,7 +14794,7 @@
       </c>
       <c r="E226" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F226" s="9" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="G226" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="G228" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15466,17 +15466,17 @@
       </c>
       <c r="E242" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F242" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G242" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15550,17 +15550,17 @@
       </c>
       <c r="E244" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F244" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G244" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15602,7 +15602,7 @@
       </c>
       <c r="G245" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19204,7 +19204,7 @@
       </c>
       <c r="E331" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F331" s="9" t="inlineStr">
@@ -19214,7 +19214,7 @@
       </c>
       <c r="G331" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19298,7 +19298,7 @@
       </c>
       <c r="G333" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19330,17 +19330,17 @@
       </c>
       <c r="E334" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F334" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G334" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19498,7 +19498,7 @@
       </c>
       <c r="E338" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F338" s="9" t="inlineStr">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="G338" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19844,7 +19844,7 @@
       </c>
       <c r="G346" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="G349" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20852,7 +20852,7 @@
       </c>
       <c r="G370" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23782,17 +23782,17 @@
       </c>
       <c r="E440" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F440" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G440" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23908,7 +23908,7 @@
       </c>
       <c r="E443" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F443" s="9" t="inlineStr">
@@ -23918,7 +23918,7 @@
       </c>
       <c r="G443" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24202,17 +24202,17 @@
       </c>
       <c r="E450" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F450" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G450" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24254,7 +24254,7 @@
       </c>
       <c r="G451" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24370,17 +24370,17 @@
       </c>
       <c r="E454" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F454" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G454" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26690,7 +26690,7 @@
       </c>
       <c r="G509" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28192,17 +28192,17 @@
       </c>
       <c r="E545" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F545" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G545" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="G556" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28790,7 +28790,7 @@
       </c>
       <c r="G559" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32528,7 +32528,7 @@
       </c>
       <c r="G648" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="G656" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33022,17 +33022,17 @@
       </c>
       <c r="E660" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F660" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G660" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33074,7 +33074,7 @@
       </c>
       <c r="G661" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="G719" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36392,7 +36392,7 @@
       </c>
       <c r="G740" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36938,7 +36938,7 @@
       </c>
       <c r="G753" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37484,7 +37484,7 @@
       </c>
       <c r="G766" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37516,17 +37516,17 @@
       </c>
       <c r="E767" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F767" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G767" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37610,7 +37610,7 @@
       </c>
       <c r="G769" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41548,17 +41548,17 @@
       </c>
       <c r="E863" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F863" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G863" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41800,17 +41800,17 @@
       </c>
       <c r="E869" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F869" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G869" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41894,7 +41894,7 @@
       </c>
       <c r="G871" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41926,17 +41926,17 @@
       </c>
       <c r="E872" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F872" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G872" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42010,7 +42010,7 @@
       </c>
       <c r="E874" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F874" s="9" t="inlineStr">
@@ -42020,7 +42020,7 @@
       </c>
       <c r="G874" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45538,7 +45538,7 @@
       </c>
       <c r="E958" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F958" s="9" t="inlineStr">
@@ -45548,7 +45548,7 @@
       </c>
       <c r="G958" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45958,17 +45958,17 @@
       </c>
       <c r="E968" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F968" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G968" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46630,7 +46630,7 @@
       </c>
       <c r="E984" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F984" s="9" t="inlineStr">
@@ -46640,7 +46640,7 @@
       </c>
       <c r="G984" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47312,7 +47312,7 @@
       </c>
       <c r="G1000" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47354,7 +47354,7 @@
       </c>
       <c r="G1001" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,21 +47455,21 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-09-21) ---</t>
+          <t>--- Daily narrative (2026-09-22) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>As of 2026-09-21: overall risk 6.7/10 (High) (Set 1 5.8/10, Set 2 5.0/10, Set 3 4.5/10, Set 4 6.5/10, Set 5 5.2/10).</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>- CRE maturity wall / regional banks: 4 -&gt; 5/10 (Elevated), up. Driver: CMBS office delinquency rate (%) now band 1; Regional-bank CRE stress (0 calm / 1 isolated / 2 cluster) now band 1.</t>
+          <t>Macro risk remains High at 6.6, with developing-world debt stabilizing but private credit opacity and Japan fiscal stress dominating the risk surface.</t>
         </is>
       </c>
     </row>
@@ -47479,7 +47479,48 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>(AI narrative unavailable: HTTP Error 400: Bad Request)</t>
+          <t>**STORY CHANGES**</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Developing-world debt crisis** moved to Elevated (was 6.0): US real yields eased 50bp, reducing refinancing pressure, though IMF program activity remains calm—practical risk is a false floor if global rates spike again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**ELEVATED OR HIGHER RISKS TO MONITOR**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Five stories sit at High: Private credit's opaque expansion (8.0), Japan fiscal/JGB/carry trade (7.0), Critical minerals as a weapon (7.0), and Sea lanes &amp; undersea cables (7.0). Eleven others at Elevated (5.0–6.0) span Treasury basis trades, China deflation, AI financing loops, CRE maturity walls, eurozone fragility, and supply-chain choke points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH CLOSEST**</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion at 8.0 (High) represents the least transparent systemic amplifier.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-22  -  generated 2026-09-22 06:18 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-22  -  generated 2026-09-22 15:40 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.614</v>
+        <v>157.466</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6964</v>
+        <v>6.6991</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>312</v>
+        <v>311.9</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4358.2998</v>
+        <v>4370.7002</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.818</v>
+        <v>6.83</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>93.58</v>
+        <v>91.39</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>14.87</v>
+        <v>14.3</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47469,7 +47469,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk remains High at 6.6, with developing-world debt stabilizing but private credit opacity and Japan fiscal stress dominating the risk surface.</t>
+          <t>Macro risk stands at High, driven by structural vulnerabilities in private credit, Japan's carry-trade exposure, and geopolitical leverage over critical inputs.</t>
         </is>
       </c>
     </row>
@@ -47479,48 +47479,69 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORY CHANGES**</t>
+          <t>**STORIES**</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>• **Developing-world debt crisis** moved to Elevated (was 6.0): US real yields eased 50bp, reducing refinancing pressure, though IMF program activity remains calm—practical risk is a false floor if global rates spike again.</t>
+          <t>No intraday level changes recorded. Persistent High-band risks remain:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• **Private credit's opaque expansion** (High): Rapid growth in unregulated lending with limited transparency creates tail-risk for sudden deleveraging.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**ELEVATED OR HIGHER RISKS TO MONITOR**</t>
+          <t>• **Japan fiscal / JGB / carry trade** (High): Sustained BoJ policy uncertainty and funding pressure amplify unwinding risk across global markets.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Five stories sit at High: Private credit's opaque expansion (8.0), Japan fiscal/JGB/carry trade (7.0), Critical minerals as a weapon (7.0), and Sea lanes &amp; undersea cables (7.0). Eleven others at Elevated (5.0–6.0) span Treasury basis trades, China deflation, AI financing loops, CRE maturity walls, eurozone fragility, and supply-chain choke points.</t>
+          <t>• **Critical minerals as a weapon** (High): State control of supply chains creates asymmetric leverage; disruption cascades into semiconductors and energy transition.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• **Sea lanes &amp; underscore cables** (High): Geopolitical tensions threaten physical infrastructure for trade and data; limited redundancy.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH CLOSEST**</t>
-        </is>
-      </c>
+      <c r="A23" s="12" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion at 8.0 (High) represents the least transparent systemic amplifier.</t>
+          <t>Five Elevated-band stories span Treasury basis trades, China spillover, CRE maturity stress, and commodity fragility. No momentum shifts observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>**WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion carries highest structural risk—opacity prevents early warning of forced liquidations.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-22  -  generated 2026-09-22 15:40 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-23  -  generated 2026-09-23 15:33 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.466</v>
+        <v>158.343</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6991</v>
+        <v>6.7011</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>311.9</v>
+        <v>312</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4370.7002</v>
+        <v>4329.3999</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.83</v>
+        <v>6.781</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>91.39</v>
+        <v>91.72</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>14.3</v>
+        <v>14.65</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5764,17 +5764,17 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G11" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5848,17 +5848,17 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="E102" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F102" s="9" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9880,7 +9880,7 @@
       </c>
       <c r="E109" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F109" s="9" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="G109" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10174,17 +10174,17 @@
       </c>
       <c r="E116" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F116" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G116" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="E205" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F205" s="9" t="inlineStr">
@@ -13922,7 +13922,7 @@
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="G207" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14584,17 +14584,17 @@
       </c>
       <c r="E221" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F221" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G221" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14668,17 +14668,17 @@
       </c>
       <c r="E223" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F223" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G223" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="G224" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="E310" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F310" s="9" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="G310" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18416,7 +18416,7 @@
       </c>
       <c r="G312" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18448,17 +18448,17 @@
       </c>
       <c r="E313" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F313" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G313" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="E317" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F317" s="9" t="inlineStr">
@@ -18626,7 +18626,7 @@
       </c>
       <c r="G317" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18962,7 +18962,7 @@
       </c>
       <c r="G325" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G328" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19970,7 +19970,7 @@
       </c>
       <c r="G349" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22900,17 +22900,17 @@
       </c>
       <c r="E419" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F419" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G419" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23026,7 +23026,7 @@
       </c>
       <c r="E422" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F422" s="9" t="inlineStr">
@@ -23036,7 +23036,7 @@
       </c>
       <c r="G422" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23320,17 +23320,17 @@
       </c>
       <c r="E429" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F429" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G429" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23372,7 +23372,7 @@
       </c>
       <c r="G430" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23488,17 +23488,17 @@
       </c>
       <c r="E433" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F433" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G433" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25808,7 +25808,7 @@
       </c>
       <c r="G488" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27310,17 +27310,17 @@
       </c>
       <c r="E524" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F524" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G524" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27782,7 +27782,7 @@
       </c>
       <c r="G535" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27908,7 +27908,7 @@
       </c>
       <c r="G538" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31646,7 +31646,7 @@
       </c>
       <c r="G627" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31982,7 +31982,7 @@
       </c>
       <c r="G635" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32140,17 +32140,17 @@
       </c>
       <c r="E639" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F639" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G639" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32192,7 +32192,7 @@
       </c>
       <c r="G640" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34628,7 +34628,7 @@
       </c>
       <c r="G698" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35510,7 +35510,7 @@
       </c>
       <c r="G719" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36056,7 +36056,7 @@
       </c>
       <c r="G732" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36602,7 +36602,7 @@
       </c>
       <c r="G745" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36634,17 +36634,17 @@
       </c>
       <c r="E746" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F746" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G746" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36728,7 +36728,7 @@
       </c>
       <c r="G748" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40666,17 +40666,17 @@
       </c>
       <c r="E842" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F842" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G842" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40918,17 +40918,17 @@
       </c>
       <c r="E848" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F848" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G848" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41012,7 +41012,7 @@
       </c>
       <c r="G850" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41044,17 +41044,17 @@
       </c>
       <c r="E851" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F851" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G851" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41128,7 +41128,7 @@
       </c>
       <c r="E853" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F853" s="9" t="inlineStr">
@@ -41138,7 +41138,7 @@
       </c>
       <c r="G853" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="E937" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F937" s="9" t="inlineStr">
@@ -44666,7 +44666,7 @@
       </c>
       <c r="G937" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45076,17 +45076,17 @@
       </c>
       <c r="E947" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F947" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G947" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45748,7 +45748,7 @@
       </c>
       <c r="E963" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F963" s="9" t="inlineStr">
@@ -45758,7 +45758,7 @@
       </c>
       <c r="G963" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46430,7 +46430,7 @@
       </c>
       <c r="G979" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46472,7 +46472,7 @@
       </c>
       <c r="G980" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,76 +47455,76 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-09-22) ---</t>
+          <t>--- Daily narrative (2026-09-23) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t>**EOD MACRO-RISK BRIEF | 23 SEPT 2026**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk stands at High, driven by structural vulnerabilities in private credit, Japan's carry-trade exposure, and geopolitical leverage over critical inputs.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Headline:** Overall macro risk remains High, with structural leverage and supply-chain weaponization as persistent fault lines.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORIES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No intraday level changes recorded. Persistent High-band risks remain:</t>
+          <t>**Key Stories at Elevated or Higher Risk:**</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High): Rapid growth in unregulated lending with limited transparency creates tail-risk for sudden deleveraging.</t>
+          <t>• **Private credit's opaque expansion** (High) – Unregulated lending channels continue rapid growth without transparent risk disclosure; systemic contagion path if redemptions accelerate.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): Sustained BoJ policy uncertainty and funding pressure amplify unwinding risk across global markets.</t>
+          <t>• **Japan fiscal / JGB / carry trade** (High) – Persistent vulnerability to yen revaluation shocks; unwinding could trigger cross-asset volatility.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon** (High): State control of supply chains creates asymmetric leverage; disruption cascades into semiconductors and energy transition.</t>
+          <t>• **Sea lanes &amp; undersea cables** (High) – Geopolitical tension over critical transit and data routes; disruption risk to global trade and communications.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; underscore cables** (High): Geopolitical tensions threaten physical infrastructure for trade and data; limited redundancy.</t>
+          <t>• **Critical minerals as a weapon** – Supply leverage asymmetry tilts policy outcomes; cost inflation in green and defense buildouts.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>• **Treasury basis trade** (Elevated) – Hidden leverage via cash-futures spreads; rapid deleveraging could spike funding costs.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>Five Elevated-band stories span Treasury basis trades, China spillover, CRE maturity stress, and commodity fragility. No momentum shifts observed.</t>
+          <t>• **China price spillover** (Elevated) – Deflationary exports and input cost pressures strain margin-dependent sectors globally.</t>
         </is>
       </c>
     </row>
@@ -47534,14 +47534,7 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>**WATCH**</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion carries highest structural risk—opacity prevents early warning of forced liquidations.</t>
+          <t>**Watch Closest:** Private credit's opaque expansion—largest absolute risk given scale and opacity.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-23  -  generated 2026-09-23 15:33 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-24  -  generated 2026-09-24 15:54 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>81.2</v>
+        <v>95.45</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.343</v>
+        <v>158.888</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.047</v>
+        <v>4.044</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.68</v>
+        <v>2.73</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7011</v>
+        <v>6.7041</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>312</v>
+        <v>312.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4329.3999</v>
+        <v>4288.1001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.781</v>
+        <v>6.7595</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>91.72</v>
+        <v>96.20999999999999</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>14.65</v>
+        <v>16.2</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>81.2</v>
+        <v>95.45</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5974,17 +5974,17 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8704,7 +8704,7 @@
       </c>
       <c r="E81" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F81" s="9" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="E88" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F88" s="9" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="G88" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9292,17 +9292,17 @@
       </c>
       <c r="E95" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F95" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13030,7 +13030,7 @@
       </c>
       <c r="E184" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F184" s="9" t="inlineStr">
@@ -13040,7 +13040,7 @@
       </c>
       <c r="G184" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="G186" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="E200" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F200" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G200" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13786,17 +13786,17 @@
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="G203" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="E289" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F289" s="9" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="G289" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17534,7 +17534,7 @@
       </c>
       <c r="G291" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17566,17 +17566,17 @@
       </c>
       <c r="E292" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F292" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G292" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17734,7 +17734,7 @@
       </c>
       <c r="E296" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F296" s="9" t="inlineStr">
@@ -17744,7 +17744,7 @@
       </c>
       <c r="G296" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="G304" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="G307" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G328" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22018,17 +22018,17 @@
       </c>
       <c r="E398" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F398" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G398" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22144,7 +22144,7 @@
       </c>
       <c r="E401" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F401" s="9" t="inlineStr">
@@ -22154,7 +22154,7 @@
       </c>
       <c r="G401" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22438,17 +22438,17 @@
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G408" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="G409" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22606,17 +22606,17 @@
       </c>
       <c r="E412" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F412" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G412" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="G467" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26428,17 +26428,17 @@
       </c>
       <c r="E503" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F503" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G503" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G517" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30764,7 +30764,7 @@
       </c>
       <c r="G606" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31100,7 +31100,7 @@
       </c>
       <c r="G614" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31258,17 +31258,17 @@
       </c>
       <c r="E618" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F618" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G618" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31310,7 +31310,7 @@
       </c>
       <c r="G619" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="G677" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34628,7 +34628,7 @@
       </c>
       <c r="G698" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35174,7 +35174,7 @@
       </c>
       <c r="G711" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35720,7 +35720,7 @@
       </c>
       <c r="G724" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35752,17 +35752,17 @@
       </c>
       <c r="E725" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F725" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G725" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35846,7 +35846,7 @@
       </c>
       <c r="G727" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39784,17 +39784,17 @@
       </c>
       <c r="E821" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F821" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G821" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40036,17 +40036,17 @@
       </c>
       <c r="E827" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F827" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G827" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40130,7 +40130,7 @@
       </c>
       <c r="G829" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40162,17 +40162,17 @@
       </c>
       <c r="E830" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F830" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G830" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40246,7 +40246,7 @@
       </c>
       <c r="E832" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F832" s="9" t="inlineStr">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="G832" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43774,7 +43774,7 @@
       </c>
       <c r="E916" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F916" s="9" t="inlineStr">
@@ -43784,7 +43784,7 @@
       </c>
       <c r="G916" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44194,17 +44194,17 @@
       </c>
       <c r="E926" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F926" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G926" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44866,7 +44866,7 @@
       </c>
       <c r="E942" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F942" s="9" t="inlineStr">
@@ -44876,7 +44876,7 @@
       </c>
       <c r="G942" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45548,7 +45548,7 @@
       </c>
       <c r="G958" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45590,7 +45590,7 @@
       </c>
       <c r="G959" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A26"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,14 +47455,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-09-23) ---</t>
+          <t>--- Daily narrative (2026-09-24) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD MACRO-RISK BRIEF | 23 SEPT 2026**</t>
+          <t>**EOD Macro-Risk Brief | 2026-09-24**</t>
         </is>
       </c>
     </row>
@@ -47472,69 +47472,83 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Headline:** Overall macro risk remains High, with structural leverage and supply-chain weaponization as persistent fault lines.</t>
+          <t>**Headline:**</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Systemic risk remains High, driven by opaque leverage in credit markets and geopolitical supply-chain weaponization.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>**Key Stories at Elevated or Higher Risk:**</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High) – Unregulated lending channels continue rapid growth without transparent risk disclosure; systemic contagion path if redemptions accelerate.</t>
+          <t>**Key Stories (No Changes Today):**</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High) – Persistent vulnerability to yen revaluation shocks; unwinding could trigger cross-asset volatility.</t>
+          <t>• **Private credit's opaque expansion** (High): Unregulated balance-sheet growth and maturity mismatches create contagion risk if redemptions accelerate.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (High) – Geopolitical tension over critical transit and data routes; disruption risk to global trade and communications.</t>
+          <t>• **Sea lanes &amp; undersea cables** (High): Geopolitical fragility threatens critical infrastructure; disruption would cascade through trade and data flows.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon** – Supply leverage asymmetry tilts policy outcomes; cost inflation in green and defense buildouts.</t>
+          <t>• **Japan fiscal / JGB / carry trade** (High): Structural imbalances and yen volatility expose leveraged positions to rapid unwinding.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Treasury basis trade** (Elevated) – Hidden leverage via cash-futures spreads; rapid deleveraging could spike funding costs.</t>
+          <t>• **Critical minerals as a weapon** (High): Supply concentration in geopolitically hostile regions creates industrial and energy-transition bottlenecks.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **China price spillover** (Elevated) – Deflationary exports and input cost pressures strain margin-dependent sectors globally.</t>
+          <t>• **Treasury basis trade** (Elevated): Hidden leverage in repos and derivatives increases rollover risk in stress scenarios.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr"/>
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>• Nine additional Elevated-level risks span emerging-market debt, China deflation, CRE, eurozone fragility, AI financing, and commodity constraints.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>**Watch Closest:** Private credit's opaque expansion—largest absolute risk given scale and opacity.</t>
+      <c r="A26" s="12" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>**Watch Most Closely:**</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion poses the highest systemic trigger—opacity prevents early detection of stress.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-09-24  -  generated 2026-09-24 15:54 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-09-25  -  generated 2026-09-25 15:55 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>95.45</v>
+        <v>104.58</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.888</v>
+        <v>157.381</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.044</v>
+        <v>4.115</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.7041</v>
+        <v>6.7123</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>312.8</v>
+        <v>312.1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4288.1001</v>
+        <v>4310.2002</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.7595</v>
+        <v>6.752</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>96.20999999999999</v>
+        <v>94.13</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>16.2</v>
+        <v>15.41</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>95.45</v>
+        <v>104.58</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="E60" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F60" s="9" t="inlineStr">
@@ -7832,7 +7832,7 @@
       </c>
       <c r="G60" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="E67" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F67" s="9" t="inlineStr">
@@ -8126,7 +8126,7 @@
       </c>
       <c r="G67" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8410,17 +8410,17 @@
       </c>
       <c r="E74" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F74" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="E163" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F163" s="9" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="G163" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="H163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="G165" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12820,17 +12820,17 @@
       </c>
       <c r="E179" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F179" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G179" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12904,17 +12904,17 @@
       </c>
       <c r="E181" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F181" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G181" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="G182" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="E268" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F268" s="9" t="inlineStr">
@@ -16568,7 +16568,7 @@
       </c>
       <c r="G268" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="G270" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16684,17 +16684,17 @@
       </c>
       <c r="E271" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F271" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="E275" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F275" s="9" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="G275" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17198,7 +17198,7 @@
       </c>
       <c r="G283" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17324,7 +17324,7 @@
       </c>
       <c r="G286" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="G307" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21136,17 +21136,17 @@
       </c>
       <c r="E377" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F377" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G377" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21262,7 +21262,7 @@
       </c>
       <c r="E380" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F380" s="9" t="inlineStr">
@@ -21272,7 +21272,7 @@
       </c>
       <c r="G380" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21556,17 +21556,17 @@
       </c>
       <c r="E387" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F387" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G387" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="G388" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21724,17 +21724,17 @@
       </c>
       <c r="E391" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F391" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G391" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24044,7 +24044,7 @@
       </c>
       <c r="G446" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25546,17 +25546,17 @@
       </c>
       <c r="E482" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F482" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G482" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26018,7 +26018,7 @@
       </c>
       <c r="G493" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26144,7 +26144,7 @@
       </c>
       <c r="G496" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29882,7 +29882,7 @@
       </c>
       <c r="G585" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30218,7 +30218,7 @@
       </c>
       <c r="G593" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30376,17 +30376,17 @@
       </c>
       <c r="E597" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F597" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G597" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30428,7 +30428,7 @@
       </c>
       <c r="G598" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32864,7 +32864,7 @@
       </c>
       <c r="G656" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33746,7 +33746,7 @@
       </c>
       <c r="G677" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34292,7 +34292,7 @@
       </c>
       <c r="G690" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34838,7 +34838,7 @@
       </c>
       <c r="G703" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34870,17 +34870,17 @@
       </c>
       <c r="E704" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F704" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G704" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34964,7 +34964,7 @@
       </c>
       <c r="G706" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38902,17 +38902,17 @@
       </c>
       <c r="E800" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F800" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G800" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39154,17 +39154,17 @@
       </c>
       <c r="E806" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F806" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G806" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39248,7 +39248,7 @@
       </c>
       <c r="G808" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39280,17 +39280,17 @@
       </c>
       <c r="E809" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F809" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G809" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39364,7 +39364,7 @@
       </c>
       <c r="E811" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F811" s="9" t="inlineStr">
@@ -39374,7 +39374,7 @@
       </c>
       <c r="G811" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42892,7 +42892,7 @@
       </c>
       <c r="E895" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F895" s="9" t="inlineStr">
@@ -42902,7 +42902,7 @@
       </c>
       <c r="G895" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43312,17 +43312,17 @@
       </c>
       <c r="E905" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F905" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G905" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -43984,7 +43984,7 @@
       </c>
       <c r="E921" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F921" s="9" t="inlineStr">
@@ -43994,7 +43994,7 @@
       </c>
       <c r="G921" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44666,7 +44666,7 @@
       </c>
       <c r="G937" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44708,7 +44708,7 @@
       </c>
       <c r="G938" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46514,7 +46514,7 @@
       </c>
       <c r="G981" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47354,7 +47354,7 @@
       </c>
       <c r="G1001" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,100 +47455,107 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-09-24) ---</t>
+          <t>--- Daily narrative (2026-09-25) ---</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**EOD Macro-Risk Brief | 2026-09-24**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands at High, driven by structural leverage and supply-chain concentration across finance and critical inputs.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>Systemic risk remains High, driven by opaque leverage in credit markets and geopolitical supply-chain weaponization.</t>
+          <t>**STORIES WITH NO LEVEL CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>No intraday moves recorded; all 15 active risks maintained positions.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>**Key Stories (No Changes Today):**</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High): Unregulated balance-sheet growth and maturity mismatches create contagion risk if redemptions accelerate.</t>
+          <t>**SUSTAINED ELEVATED &amp; HIGH RISKS**</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (High): Geopolitical fragility threatens critical infrastructure; disruption would cascade through trade and data flows.</t>
+          <t>- **Private credit's opaque expansion** (High): Continued unregulated growth with limited visibility into counterparty stress and redemption dynamics.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): Structural imbalances and yen volatility expose leveraged positions to rapid unwinding.</t>
+          <t>- **Japan fiscal / JGB / carry trade** (High): Persistent vulnerability to yen revaluation triggering forced unwinding in leveraged positions.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **Critical minerals as a weapon** (High): Supply concentration in geopolitically hostile regions creates industrial and energy-transition bottlenecks.</t>
+          <t>- **Sea lanes &amp; undersea cables** (High): Geopolitical friction and infrastructure fragility remain acute chokepoints for global trade and data flows.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>• **Treasury basis trade** (Elevated): Hidden leverage in repos and derivatives increases rollover risk in stress scenarios.</t>
+          <t>- **Critical minerals as a weapon** (High): Supply weaponization sustained; no resolution in dependency de-risking.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• Nine additional Elevated-level risks span emerging-market debt, China deflation, CRE, eurozone fragility, AI financing, and commodity constraints.</t>
+          <t>- **Treasury basis trade** (Elevated): Hidden leverage embedded in repo markets; potential flash event vector.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>- Nine additional Elevated risks span sovereign debt, China deflation spillover, AI financing loops, and commodity input fragility.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>**Watch Most Closely:**</t>
-        </is>
-      </c>
+      <c r="A27" s="12" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion poses the highest systemic trigger—opacity prevents early detection of stress.</t>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion requires urgent stress-test transparency given systemic reach and redemption uncertainty.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-10-08  -  generated 2026-10-08 17:58 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-10-09  -  generated 2026-10-09 17:32 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>99.81010000000001</v>
+        <v>99.55719999999999</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>157.737</v>
+        <v>158.274</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>4.148</v>
+        <v>4.136</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         </is>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6939</v>
+        <v>6.682</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>313.1</v>
+        <v>311.5</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4153.7002</v>
+        <v>4219.1001</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.5665</v>
+        <v>6.6955</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>91.63</v>
+        <v>91.31</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.85</v>
+        <v>14.88</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>99.81010000000001</v>
+        <v>99.55719999999999</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
     <row r="2">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -5408,7 +5408,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -5450,7 +5450,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -5534,7 +5534,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -5576,7 +5576,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -5618,7 +5618,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -5660,7 +5660,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -5702,7 +5702,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -5744,7 +5744,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -5786,7 +5786,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -5828,7 +5828,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
@@ -5870,7 +5870,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -5912,7 +5912,7 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -5954,7 +5954,7 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -6038,7 +6038,7 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -6080,7 +6080,7 @@
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -6122,7 +6122,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -6164,7 +6164,7 @@
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
@@ -6248,7 +6248,7 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -6290,7 +6290,7 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -6332,7 +6332,7 @@
     <row r="25">
       <c r="A25" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -6374,7 +6374,7 @@
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -6416,7 +6416,7 @@
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -6458,7 +6458,7 @@
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -6500,7 +6500,7 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
@@ -6584,7 +6584,7 @@
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -6668,7 +6668,7 @@
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -6710,7 +6710,7 @@
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -6752,7 +6752,7 @@
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -6794,7 +6794,7 @@
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -6878,7 +6878,7 @@
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -6920,7 +6920,7 @@
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -6962,7 +6962,7 @@
     <row r="40">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -7004,7 +7004,7 @@
     <row r="41">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -7088,7 +7088,7 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B43" s="9" t="inlineStr">
@@ -7130,7 +7130,7 @@
     <row r="44">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
@@ -7172,7 +7172,7 @@
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
@@ -7214,7 +7214,7 @@
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B46" s="9" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
@@ -7298,7 +7298,7 @@
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
@@ -7340,7 +7340,7 @@
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
@@ -7382,7 +7382,7 @@
     <row r="50">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
@@ -7424,7 +7424,7 @@
     <row r="51">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
@@ -7466,7 +7466,7 @@
     <row r="52">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
@@ -7508,7 +7508,7 @@
     <row r="53">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
@@ -7550,7 +7550,7 @@
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
@@ -7592,7 +7592,7 @@
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
@@ -7634,7 +7634,7 @@
     <row r="56">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
@@ -7676,7 +7676,7 @@
     <row r="57">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
@@ -7718,7 +7718,7 @@
     <row r="58">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
@@ -7760,7 +7760,7 @@
     <row r="59">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
@@ -7802,7 +7802,7 @@
     <row r="60">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
@@ -7844,7 +7844,7 @@
     <row r="61">
       <c r="A61" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B61" s="9" t="inlineStr">
@@ -7886,7 +7886,7 @@
     <row r="62">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -7928,7 +7928,7 @@
     <row r="63">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="64">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
@@ -8012,7 +8012,7 @@
     <row r="65">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
@@ -8054,7 +8054,7 @@
     <row r="66">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="67">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
@@ -8138,7 +8138,7 @@
     <row r="68">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
@@ -8180,7 +8180,7 @@
     <row r="69">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
@@ -8222,7 +8222,7 @@
     <row r="70">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
@@ -8264,7 +8264,7 @@
     <row r="71">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
@@ -8306,7 +8306,7 @@
     <row r="72">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
@@ -8348,7 +8348,7 @@
     <row r="73">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
@@ -8390,7 +8390,7 @@
     <row r="74">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
@@ -8432,7 +8432,7 @@
     <row r="75">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
@@ -8474,7 +8474,7 @@
     <row r="76">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
@@ -8516,7 +8516,7 @@
     <row r="77">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
@@ -8558,7 +8558,7 @@
     <row r="78">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
@@ -8600,7 +8600,7 @@
     <row r="79">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
@@ -8620,7 +8620,7 @@
       </c>
       <c r="E79" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F79" s="9" t="inlineStr">
@@ -8630,7 +8630,7 @@
       </c>
       <c r="G79" s="9" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H79" s="9" t="inlineStr">
@@ -8642,7 +8642,7 @@
     <row r="80">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
@@ -8684,7 +8684,7 @@
     <row r="81">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
@@ -8714,7 +8714,7 @@
       </c>
       <c r="G81" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H81" s="9" t="inlineStr">
@@ -8726,7 +8726,7 @@
     <row r="82">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="E82" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -8768,7 +8768,7 @@
     <row r="83">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
@@ -8810,7 +8810,7 @@
     <row r="84">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
@@ -8852,7 +8852,7 @@
     <row r="85">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
@@ -8894,7 +8894,7 @@
     <row r="86">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="E86" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F86" s="9" t="inlineStr">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
@@ -8936,7 +8936,7 @@
     <row r="87">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
@@ -8978,7 +8978,7 @@
     <row r="88">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
@@ -9020,7 +9020,7 @@
     <row r="89">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
@@ -9062,7 +9062,7 @@
     <row r="90">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
@@ -9104,7 +9104,7 @@
     <row r="91">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="92">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
@@ -9188,7 +9188,7 @@
     <row r="93">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
@@ -9230,7 +9230,7 @@
     <row r="94">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
@@ -9272,7 +9272,7 @@
     <row r="95">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
@@ -9314,7 +9314,7 @@
     <row r="96">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
@@ -9356,7 +9356,7 @@
     <row r="97">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="G97" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H97" s="9" t="inlineStr">
@@ -9398,7 +9398,7 @@
     <row r="98">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
@@ -9440,7 +9440,7 @@
     <row r="99">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
@@ -9482,7 +9482,7 @@
     <row r="100">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
@@ -9524,7 +9524,7 @@
     <row r="101">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
@@ -9566,7 +9566,7 @@
     <row r="102">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
@@ -9608,7 +9608,7 @@
     <row r="103">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
@@ -9650,7 +9650,7 @@
     <row r="104">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
@@ -9692,7 +9692,7 @@
     <row r="105">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
@@ -9734,7 +9734,7 @@
     <row r="106">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
@@ -9776,7 +9776,7 @@
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
@@ -9818,7 +9818,7 @@
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
@@ -9860,7 +9860,7 @@
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
@@ -9902,7 +9902,7 @@
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
@@ -9944,7 +9944,7 @@
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
@@ -9986,7 +9986,7 @@
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
@@ -10028,7 +10028,7 @@
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
@@ -10070,7 +10070,7 @@
     <row r="114">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
@@ -10112,7 +10112,7 @@
     <row r="115">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
@@ -10154,7 +10154,7 @@
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
@@ -10238,7 +10238,7 @@
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="G118" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
@@ -10280,7 +10280,7 @@
     <row r="119">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
@@ -10322,7 +10322,7 @@
     <row r="120">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
@@ -10364,7 +10364,7 @@
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
@@ -10406,7 +10406,7 @@
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="123">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
@@ -10490,7 +10490,7 @@
     <row r="124">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
@@ -10532,7 +10532,7 @@
     <row r="125">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="126">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
@@ -10616,7 +10616,7 @@
     <row r="127">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
@@ -10658,7 +10658,7 @@
     <row r="128">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
@@ -10700,7 +10700,7 @@
     <row r="129">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
@@ -10742,7 +10742,7 @@
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
@@ -10784,7 +10784,7 @@
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
@@ -10826,7 +10826,7 @@
     <row r="132">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
@@ -10868,7 +10868,7 @@
     <row r="133">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
@@ -10910,7 +10910,7 @@
     <row r="134">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
@@ -10952,7 +10952,7 @@
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B135" s="9" t="inlineStr">
@@ -10994,7 +10994,7 @@
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B136" s="9" t="inlineStr">
@@ -11036,7 +11036,7 @@
     <row r="137">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
@@ -11078,7 +11078,7 @@
     <row r="138">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
@@ -11120,7 +11120,7 @@
     <row r="139">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="140">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
@@ -11204,7 +11204,7 @@
     <row r="141">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="142">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
@@ -11288,7 +11288,7 @@
     <row r="143">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
@@ -11330,7 +11330,7 @@
     <row r="144">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
@@ -11372,7 +11372,7 @@
     <row r="145">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
@@ -11414,7 +11414,7 @@
     <row r="146">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
@@ -11456,7 +11456,7 @@
     <row r="147">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
@@ -11498,7 +11498,7 @@
     <row r="148">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
@@ -11540,7 +11540,7 @@
     <row r="149">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
@@ -11582,7 +11582,7 @@
     <row r="150">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
@@ -11624,7 +11624,7 @@
     <row r="151">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
@@ -11666,7 +11666,7 @@
     <row r="152">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
@@ -11708,7 +11708,7 @@
     <row r="153">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
@@ -11750,7 +11750,7 @@
     <row r="154">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
@@ -11792,7 +11792,7 @@
     <row r="155">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
@@ -11834,7 +11834,7 @@
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="157">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
@@ -11918,7 +11918,7 @@
     <row r="158">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
@@ -11960,7 +11960,7 @@
     <row r="159">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
@@ -12002,7 +12002,7 @@
     <row r="160">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
@@ -12044,7 +12044,7 @@
     <row r="161">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
@@ -12086,7 +12086,7 @@
     <row r="162">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
@@ -12128,7 +12128,7 @@
     <row r="163">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
@@ -12170,7 +12170,7 @@
     <row r="164">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
@@ -12212,7 +12212,7 @@
     <row r="165">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
@@ -12254,7 +12254,7 @@
     <row r="166">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
     <row r="167">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
@@ -12338,7 +12338,7 @@
     <row r="168">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
@@ -12380,7 +12380,7 @@
     <row r="169">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
@@ -12422,7 +12422,7 @@
     <row r="170">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
@@ -12464,7 +12464,7 @@
     <row r="171">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
@@ -12506,7 +12506,7 @@
     <row r="172">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
@@ -12548,7 +12548,7 @@
     <row r="173">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
@@ -12590,7 +12590,7 @@
     <row r="174">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
@@ -12632,7 +12632,7 @@
     <row r="175">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
@@ -12674,7 +12674,7 @@
     <row r="176">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
@@ -12716,7 +12716,7 @@
     <row r="177">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
@@ -12758,7 +12758,7 @@
     <row r="178">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
@@ -12800,7 +12800,7 @@
     <row r="179">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
@@ -12842,7 +12842,7 @@
     <row r="180">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
@@ -12884,7 +12884,7 @@
     <row r="181">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
@@ -12926,7 +12926,7 @@
     <row r="182">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
@@ -12968,7 +12968,7 @@
     <row r="183">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
@@ -13010,7 +13010,7 @@
     <row r="184">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
@@ -13052,7 +13052,7 @@
     <row r="185">
       <c r="A185" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B185" s="9" t="inlineStr">
@@ -13094,7 +13094,7 @@
     <row r="186">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
@@ -13136,7 +13136,7 @@
     <row r="187">
       <c r="A187" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B187" s="9" t="inlineStr">
@@ -13178,7 +13178,7 @@
     <row r="188">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
@@ -13198,17 +13198,17 @@
       </c>
       <c r="E188" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F188" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G188" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H188" s="9" t="inlineStr">
@@ -13220,7 +13220,7 @@
     <row r="189">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
@@ -13262,7 +13262,7 @@
     <row r="190">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="191">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="E191" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F191" s="9" t="inlineStr">
@@ -13334,7 +13334,7 @@
       </c>
       <c r="G191" s="9" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H191" s="9" t="inlineStr">
@@ -13346,7 +13346,7 @@
     <row r="192">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
@@ -13388,7 +13388,7 @@
     <row r="193">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
@@ -13430,7 +13430,7 @@
     <row r="194">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
@@ -13472,7 +13472,7 @@
     <row r="195">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
@@ -13514,7 +13514,7 @@
     <row r="196">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
@@ -13556,7 +13556,7 @@
     <row r="197">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
@@ -13598,7 +13598,7 @@
     <row r="198">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
@@ -13618,17 +13618,17 @@
       </c>
       <c r="E198" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F198" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G198" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H198" s="9" t="inlineStr">
@@ -13640,7 +13640,7 @@
     <row r="199">
       <c r="A199" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B199" s="9" t="inlineStr">
@@ -13670,7 +13670,7 @@
       </c>
       <c r="G199" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="H199" s="9" t="inlineStr">
@@ -13682,7 +13682,7 @@
     <row r="200">
       <c r="A200" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B200" s="9" t="inlineStr">
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B201" s="9" t="inlineStr">
@@ -13766,7 +13766,7 @@
     <row r="202">
       <c r="A202" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B202" s="9" t="inlineStr">
@@ -13786,17 +13786,17 @@
       </c>
       <c r="E202" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F202" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G202" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H202" s="9" t="inlineStr">
@@ -13808,7 +13808,7 @@
     <row r="203">
       <c r="A203" s="9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B203" s="9" t="inlineStr">
@@ -13850,7 +13850,7 @@
     <row r="204">
       <c r="A204" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B204" s="9" t="inlineStr">
@@ -13892,7 +13892,7 @@
     <row r="205">
       <c r="A205" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B205" s="9" t="inlineStr">
@@ -13934,7 +13934,7 @@
     <row r="206">
       <c r="A206" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B206" s="9" t="inlineStr">
@@ -13976,7 +13976,7 @@
     <row r="207">
       <c r="A207" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B207" s="9" t="inlineStr">
@@ -14018,7 +14018,7 @@
     <row r="208">
       <c r="A208" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B208" s="9" t="inlineStr">
@@ -14060,7 +14060,7 @@
     <row r="209">
       <c r="A209" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B209" s="9" t="inlineStr">
@@ -14102,7 +14102,7 @@
     <row r="210">
       <c r="A210" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B210" s="9" t="inlineStr">
@@ -14144,7 +14144,7 @@
     <row r="211">
       <c r="A211" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B211" s="9" t="inlineStr">
@@ -14186,7 +14186,7 @@
     <row r="212">
       <c r="A212" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B212" s="9" t="inlineStr">
@@ -14228,7 +14228,7 @@
     <row r="213">
       <c r="A213" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B213" s="9" t="inlineStr">
@@ -14270,7 +14270,7 @@
     <row r="214">
       <c r="A214" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B214" s="9" t="inlineStr">
@@ -14312,7 +14312,7 @@
     <row r="215">
       <c r="A215" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B215" s="9" t="inlineStr">
@@ -14354,7 +14354,7 @@
     <row r="216">
       <c r="A216" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B216" s="9" t="inlineStr">
@@ -14396,7 +14396,7 @@
     <row r="217">
       <c r="A217" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B217" s="9" t="inlineStr">
@@ -14438,7 +14438,7 @@
     <row r="218">
       <c r="A218" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B218" s="9" t="inlineStr">
@@ -14480,7 +14480,7 @@
     <row r="219">
       <c r="A219" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B219" s="9" t="inlineStr">
@@ -14522,7 +14522,7 @@
     <row r="220">
       <c r="A220" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B220" s="9" t="inlineStr">
@@ -14564,7 +14564,7 @@
     <row r="221">
       <c r="A221" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B221" s="9" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="222">
       <c r="A222" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B222" s="9" t="inlineStr">
@@ -14648,7 +14648,7 @@
     <row r="223">
       <c r="A223" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B223" s="9" t="inlineStr">
@@ -14690,7 +14690,7 @@
     <row r="224">
       <c r="A224" s="9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B224" s="9" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="225">
       <c r="A225" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B225" s="9" t="inlineStr">
@@ -14774,7 +14774,7 @@
     <row r="226">
       <c r="A226" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B226" s="9" t="inlineStr">
@@ -14816,7 +14816,7 @@
     <row r="227">
       <c r="A227" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B227" s="9" t="inlineStr">
@@ -14858,7 +14858,7 @@
     <row r="228">
       <c r="A228" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B228" s="9" t="inlineStr">
@@ -14900,7 +14900,7 @@
     <row r="229">
       <c r="A229" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr">
@@ -14942,7 +14942,7 @@
     <row r="230">
       <c r="A230" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B230" s="9" t="inlineStr">
@@ -14984,7 +14984,7 @@
     <row r="231">
       <c r="A231" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B231" s="9" t="inlineStr">
@@ -15026,7 +15026,7 @@
     <row r="232">
       <c r="A232" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B232" s="9" t="inlineStr">
@@ -15068,7 +15068,7 @@
     <row r="233">
       <c r="A233" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B233" s="9" t="inlineStr">
@@ -15110,7 +15110,7 @@
     <row r="234">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
@@ -15152,7 +15152,7 @@
     <row r="235">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
@@ -15194,7 +15194,7 @@
     <row r="236">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
@@ -15236,7 +15236,7 @@
     <row r="237">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
@@ -15278,7 +15278,7 @@
     <row r="238">
       <c r="A238" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B238" s="9" t="inlineStr">
@@ -15320,7 +15320,7 @@
     <row r="239">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
@@ -15362,7 +15362,7 @@
     <row r="240">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
@@ -15404,7 +15404,7 @@
     <row r="241">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
@@ -15446,7 +15446,7 @@
     <row r="242">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
@@ -15488,7 +15488,7 @@
     <row r="243">
       <c r="A243" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B243" s="9" t="inlineStr">
@@ -15530,7 +15530,7 @@
     <row r="244">
       <c r="A244" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B244" s="9" t="inlineStr">
@@ -15572,7 +15572,7 @@
     <row r="245">
       <c r="A245" s="9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B245" s="9" t="inlineStr">
@@ -15614,7 +15614,7 @@
     <row r="246">
       <c r="A246" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B246" s="9" t="inlineStr">
@@ -15656,7 +15656,7 @@
     <row r="247">
       <c r="A247" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B247" s="9" t="inlineStr">
@@ -15698,7 +15698,7 @@
     <row r="248">
       <c r="A248" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B248" s="9" t="inlineStr">
@@ -15740,7 +15740,7 @@
     <row r="249">
       <c r="A249" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B249" s="9" t="inlineStr">
@@ -15782,7 +15782,7 @@
     <row r="250">
       <c r="A250" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B250" s="9" t="inlineStr">
@@ -15824,7 +15824,7 @@
     <row r="251">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
@@ -15866,7 +15866,7 @@
     <row r="252">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
@@ -15908,7 +15908,7 @@
     <row r="253">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
@@ -15950,7 +15950,7 @@
     <row r="254">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
@@ -15992,7 +15992,7 @@
     <row r="255">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
@@ -16034,7 +16034,7 @@
     <row r="256">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
@@ -16076,7 +16076,7 @@
     <row r="257">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
@@ -16106,7 +16106,7 @@
       </c>
       <c r="G257" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H257" s="9" t="inlineStr">
@@ -16118,7 +16118,7 @@
     <row r="258">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
@@ -16160,7 +16160,7 @@
     <row r="259">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
@@ -16202,7 +16202,7 @@
     <row r="260">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
@@ -16244,7 +16244,7 @@
     <row r="261">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
@@ -16286,7 +16286,7 @@
     <row r="262">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
@@ -16328,7 +16328,7 @@
     <row r="263">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
@@ -16370,7 +16370,7 @@
     <row r="264">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
@@ -16412,7 +16412,7 @@
     <row r="265">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
@@ -16454,7 +16454,7 @@
     <row r="266">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
@@ -16496,7 +16496,7 @@
     <row r="267">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
@@ -16538,7 +16538,7 @@
     <row r="268">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
@@ -16580,7 +16580,7 @@
     <row r="269">
       <c r="A269" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B269" s="9" t="inlineStr">
@@ -16622,7 +16622,7 @@
     <row r="270">
       <c r="A270" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B270" s="9" t="inlineStr">
@@ -16664,7 +16664,7 @@
     <row r="271">
       <c r="A271" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B271" s="9" t="inlineStr">
@@ -16706,7 +16706,7 @@
     <row r="272">
       <c r="A272" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B272" s="9" t="inlineStr">
@@ -16748,7 +16748,7 @@
     <row r="273">
       <c r="A273" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B273" s="9" t="inlineStr">
@@ -16790,7 +16790,7 @@
     <row r="274">
       <c r="A274" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B274" s="9" t="inlineStr">
@@ -16832,7 +16832,7 @@
     <row r="275">
       <c r="A275" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B275" s="9" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="276">
       <c r="A276" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B276" s="9" t="inlineStr">
@@ -16916,7 +16916,7 @@
     <row r="277">
       <c r="A277" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B277" s="9" t="inlineStr">
@@ -16958,7 +16958,7 @@
     <row r="278">
       <c r="A278" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B278" s="9" t="inlineStr">
@@ -17000,7 +17000,7 @@
     <row r="279">
       <c r="A279" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B279" s="9" t="inlineStr">
@@ -17042,7 +17042,7 @@
     <row r="280">
       <c r="A280" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B280" s="9" t="inlineStr">
@@ -17084,7 +17084,7 @@
     <row r="281">
       <c r="A281" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B281" s="9" t="inlineStr">
@@ -17126,7 +17126,7 @@
     <row r="282">
       <c r="A282" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B282" s="9" t="inlineStr">
@@ -17168,7 +17168,7 @@
     <row r="283">
       <c r="A283" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B283" s="9" t="inlineStr">
@@ -17210,7 +17210,7 @@
     <row r="284">
       <c r="A284" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B284" s="9" t="inlineStr">
@@ -17252,7 +17252,7 @@
     <row r="285">
       <c r="A285" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B285" s="9" t="inlineStr">
@@ -17294,7 +17294,7 @@
     <row r="286">
       <c r="A286" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B286" s="9" t="inlineStr">
@@ -17336,7 +17336,7 @@
     <row r="287">
       <c r="A287" s="9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B287" s="9" t="inlineStr">
@@ -17378,7 +17378,7 @@
     <row r="288">
       <c r="A288" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B288" s="9" t="inlineStr">
@@ -17420,7 +17420,7 @@
     <row r="289">
       <c r="A289" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B289" s="9" t="inlineStr">
@@ -17462,7 +17462,7 @@
     <row r="290">
       <c r="A290" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B290" s="9" t="inlineStr">
@@ -17504,7 +17504,7 @@
     <row r="291">
       <c r="A291" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B291" s="9" t="inlineStr">
@@ -17546,7 +17546,7 @@
     <row r="292">
       <c r="A292" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B292" s="9" t="inlineStr">
@@ -17588,7 +17588,7 @@
     <row r="293">
       <c r="A293" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B293" s="9" t="inlineStr">
@@ -17608,17 +17608,17 @@
       </c>
       <c r="E293" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F293" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G293" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H293" s="9" t="inlineStr">
@@ -17630,7 +17630,7 @@
     <row r="294">
       <c r="A294" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B294" s="9" t="inlineStr">
@@ -17672,7 +17672,7 @@
     <row r="295">
       <c r="A295" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B295" s="9" t="inlineStr">
@@ -17714,7 +17714,7 @@
     <row r="296">
       <c r="A296" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B296" s="9" t="inlineStr">
@@ -17756,7 +17756,7 @@
     <row r="297">
       <c r="A297" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B297" s="9" t="inlineStr">
@@ -17798,7 +17798,7 @@
     <row r="298">
       <c r="A298" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B298" s="9" t="inlineStr">
@@ -17840,7 +17840,7 @@
     <row r="299">
       <c r="A299" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B299" s="9" t="inlineStr">
@@ -17882,7 +17882,7 @@
     <row r="300">
       <c r="A300" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B300" s="9" t="inlineStr">
@@ -17924,7 +17924,7 @@
     <row r="301">
       <c r="A301" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B301" s="9" t="inlineStr">
@@ -17966,7 +17966,7 @@
     <row r="302">
       <c r="A302" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B302" s="9" t="inlineStr">
@@ -18008,7 +18008,7 @@
     <row r="303">
       <c r="A303" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B303" s="9" t="inlineStr">
@@ -18050,7 +18050,7 @@
     <row r="304">
       <c r="A304" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B304" s="9" t="inlineStr">
@@ -18080,7 +18080,7 @@
       </c>
       <c r="G304" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H304" s="9" t="inlineStr">
@@ -18092,7 +18092,7 @@
     <row r="305">
       <c r="A305" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B305" s="9" t="inlineStr">
@@ -18134,7 +18134,7 @@
     <row r="306">
       <c r="A306" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B306" s="9" t="inlineStr">
@@ -18176,7 +18176,7 @@
     <row r="307">
       <c r="A307" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B307" s="9" t="inlineStr">
@@ -18206,7 +18206,7 @@
       </c>
       <c r="G307" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H307" s="9" t="inlineStr">
@@ -18218,7 +18218,7 @@
     <row r="308">
       <c r="A308" s="9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B308" s="9" t="inlineStr">
@@ -18260,7 +18260,7 @@
     <row r="309">
       <c r="A309" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B309" s="9" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="310">
       <c r="A310" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B310" s="9" t="inlineStr">
@@ -18344,7 +18344,7 @@
     <row r="311">
       <c r="A311" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B311" s="9" t="inlineStr">
@@ -18386,7 +18386,7 @@
     <row r="312">
       <c r="A312" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B312" s="9" t="inlineStr">
@@ -18428,7 +18428,7 @@
     <row r="313">
       <c r="A313" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B313" s="9" t="inlineStr">
@@ -18470,7 +18470,7 @@
     <row r="314">
       <c r="A314" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B314" s="9" t="inlineStr">
@@ -18512,7 +18512,7 @@
     <row r="315">
       <c r="A315" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B315" s="9" t="inlineStr">
@@ -18554,7 +18554,7 @@
     <row r="316">
       <c r="A316" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B316" s="9" t="inlineStr">
@@ -18596,7 +18596,7 @@
     <row r="317">
       <c r="A317" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B317" s="9" t="inlineStr">
@@ -18638,7 +18638,7 @@
     <row r="318">
       <c r="A318" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B318" s="9" t="inlineStr">
@@ -18680,7 +18680,7 @@
     <row r="319">
       <c r="A319" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B319" s="9" t="inlineStr">
@@ -18722,7 +18722,7 @@
     <row r="320">
       <c r="A320" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B320" s="9" t="inlineStr">
@@ -18764,7 +18764,7 @@
     <row r="321">
       <c r="A321" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B321" s="9" t="inlineStr">
@@ -18806,7 +18806,7 @@
     <row r="322">
       <c r="A322" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B322" s="9" t="inlineStr">
@@ -18848,7 +18848,7 @@
     <row r="323">
       <c r="A323" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B323" s="9" t="inlineStr">
@@ -18890,7 +18890,7 @@
     <row r="324">
       <c r="A324" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B324" s="9" t="inlineStr">
@@ -18932,7 +18932,7 @@
     <row r="325">
       <c r="A325" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B325" s="9" t="inlineStr">
@@ -18974,7 +18974,7 @@
     <row r="326">
       <c r="A326" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B326" s="9" t="inlineStr">
@@ -19016,7 +19016,7 @@
     <row r="327">
       <c r="A327" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B327" s="9" t="inlineStr">
@@ -19058,7 +19058,7 @@
     <row r="328">
       <c r="A328" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B328" s="9" t="inlineStr">
@@ -19100,7 +19100,7 @@
     <row r="329">
       <c r="A329" s="9" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B329" s="9" t="inlineStr">
@@ -19142,7 +19142,7 @@
     <row r="330">
       <c r="A330" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B330" s="9" t="inlineStr">
@@ -19184,7 +19184,7 @@
     <row r="331">
       <c r="A331" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B331" s="9" t="inlineStr">
@@ -19226,7 +19226,7 @@
     <row r="332">
       <c r="A332" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B332" s="9" t="inlineStr">
@@ -19268,7 +19268,7 @@
     <row r="333">
       <c r="A333" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B333" s="9" t="inlineStr">
@@ -19310,7 +19310,7 @@
     <row r="334">
       <c r="A334" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B334" s="9" t="inlineStr">
@@ -19352,7 +19352,7 @@
     <row r="335">
       <c r="A335" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B335" s="9" t="inlineStr">
@@ -19394,7 +19394,7 @@
     <row r="336">
       <c r="A336" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B336" s="9" t="inlineStr">
@@ -19436,7 +19436,7 @@
     <row r="337">
       <c r="A337" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B337" s="9" t="inlineStr">
@@ -19478,7 +19478,7 @@
     <row r="338">
       <c r="A338" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B338" s="9" t="inlineStr">
@@ -19520,7 +19520,7 @@
     <row r="339">
       <c r="A339" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B339" s="9" t="inlineStr">
@@ -19562,7 +19562,7 @@
     <row r="340">
       <c r="A340" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B340" s="9" t="inlineStr">
@@ -19604,7 +19604,7 @@
     <row r="341">
       <c r="A341" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B341" s="9" t="inlineStr">
@@ -19646,7 +19646,7 @@
     <row r="342">
       <c r="A342" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B342" s="9" t="inlineStr">
@@ -19688,7 +19688,7 @@
     <row r="343">
       <c r="A343" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B343" s="9" t="inlineStr">
@@ -19730,7 +19730,7 @@
     <row r="344">
       <c r="A344" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B344" s="9" t="inlineStr">
@@ -19772,7 +19772,7 @@
     <row r="345">
       <c r="A345" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B345" s="9" t="inlineStr">
@@ -19814,7 +19814,7 @@
     <row r="346">
       <c r="A346" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B346" s="9" t="inlineStr">
@@ -19856,7 +19856,7 @@
     <row r="347">
       <c r="A347" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B347" s="9" t="inlineStr">
@@ -19898,7 +19898,7 @@
     <row r="348">
       <c r="A348" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B348" s="9" t="inlineStr">
@@ -19940,7 +19940,7 @@
     <row r="349">
       <c r="A349" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B349" s="9" t="inlineStr">
@@ -19982,7 +19982,7 @@
     <row r="350">
       <c r="A350" s="9" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B350" s="9" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="351">
       <c r="A351" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B351" s="9" t="inlineStr">
@@ -20066,7 +20066,7 @@
     <row r="352">
       <c r="A352" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B352" s="9" t="inlineStr">
@@ -20108,7 +20108,7 @@
     <row r="353">
       <c r="A353" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B353" s="9" t="inlineStr">
@@ -20150,7 +20150,7 @@
     <row r="354">
       <c r="A354" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B354" s="9" t="inlineStr">
@@ -20192,7 +20192,7 @@
     <row r="355">
       <c r="A355" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B355" s="9" t="inlineStr">
@@ -20234,7 +20234,7 @@
     <row r="356">
       <c r="A356" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B356" s="9" t="inlineStr">
@@ -20276,7 +20276,7 @@
     <row r="357">
       <c r="A357" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B357" s="9" t="inlineStr">
@@ -20318,7 +20318,7 @@
     <row r="358">
       <c r="A358" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B358" s="9" t="inlineStr">
@@ -20360,7 +20360,7 @@
     <row r="359">
       <c r="A359" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B359" s="9" t="inlineStr">
@@ -20402,7 +20402,7 @@
     <row r="360">
       <c r="A360" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B360" s="9" t="inlineStr">
@@ -20444,7 +20444,7 @@
     <row r="361">
       <c r="A361" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B361" s="9" t="inlineStr">
@@ -20486,7 +20486,7 @@
     <row r="362">
       <c r="A362" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B362" s="9" t="inlineStr">
@@ -20528,7 +20528,7 @@
     <row r="363">
       <c r="A363" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B363" s="9" t="inlineStr">
@@ -20570,7 +20570,7 @@
     <row r="364">
       <c r="A364" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B364" s="9" t="inlineStr">
@@ -20612,7 +20612,7 @@
     <row r="365">
       <c r="A365" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B365" s="9" t="inlineStr">
@@ -20654,7 +20654,7 @@
     <row r="366">
       <c r="A366" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B366" s="9" t="inlineStr">
@@ -20696,7 +20696,7 @@
     <row r="367">
       <c r="A367" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B367" s="9" t="inlineStr">
@@ -20738,7 +20738,7 @@
     <row r="368">
       <c r="A368" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B368" s="9" t="inlineStr">
@@ -20780,7 +20780,7 @@
     <row r="369">
       <c r="A369" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B369" s="9" t="inlineStr">
@@ -20822,7 +20822,7 @@
     <row r="370">
       <c r="A370" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B370" s="9" t="inlineStr">
@@ -20864,7 +20864,7 @@
     <row r="371">
       <c r="A371" s="9" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B371" s="9" t="inlineStr">
@@ -20906,7 +20906,7 @@
     <row r="372">
       <c r="A372" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B372" s="9" t="inlineStr">
@@ -20948,7 +20948,7 @@
     <row r="373">
       <c r="A373" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B373" s="9" t="inlineStr">
@@ -20990,7 +20990,7 @@
     <row r="374">
       <c r="A374" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B374" s="9" t="inlineStr">
@@ -21032,7 +21032,7 @@
     <row r="375">
       <c r="A375" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B375" s="9" t="inlineStr">
@@ -21074,7 +21074,7 @@
     <row r="376">
       <c r="A376" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B376" s="9" t="inlineStr">
@@ -21116,7 +21116,7 @@
     <row r="377">
       <c r="A377" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B377" s="9" t="inlineStr">
@@ -21158,7 +21158,7 @@
     <row r="378">
       <c r="A378" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B378" s="9" t="inlineStr">
@@ -21200,7 +21200,7 @@
     <row r="379">
       <c r="A379" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B379" s="9" t="inlineStr">
@@ -21242,7 +21242,7 @@
     <row r="380">
       <c r="A380" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B380" s="9" t="inlineStr">
@@ -21284,7 +21284,7 @@
     <row r="381">
       <c r="A381" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B381" s="9" t="inlineStr">
@@ -21326,7 +21326,7 @@
     <row r="382">
       <c r="A382" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B382" s="9" t="inlineStr">
@@ -21368,7 +21368,7 @@
     <row r="383">
       <c r="A383" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B383" s="9" t="inlineStr">
@@ -21410,7 +21410,7 @@
     <row r="384">
       <c r="A384" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B384" s="9" t="inlineStr">
@@ -21452,7 +21452,7 @@
     <row r="385">
       <c r="A385" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B385" s="9" t="inlineStr">
@@ -21494,7 +21494,7 @@
     <row r="386">
       <c r="A386" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B386" s="9" t="inlineStr">
@@ -21536,7 +21536,7 @@
     <row r="387">
       <c r="A387" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B387" s="9" t="inlineStr">
@@ -21578,7 +21578,7 @@
     <row r="388">
       <c r="A388" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B388" s="9" t="inlineStr">
@@ -21620,7 +21620,7 @@
     <row r="389">
       <c r="A389" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B389" s="9" t="inlineStr">
@@ -21662,7 +21662,7 @@
     <row r="390">
       <c r="A390" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B390" s="9" t="inlineStr">
@@ -21704,7 +21704,7 @@
     <row r="391">
       <c r="A391" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B391" s="9" t="inlineStr">
@@ -21746,7 +21746,7 @@
     <row r="392">
       <c r="A392" s="9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B392" s="9" t="inlineStr">
@@ -21788,7 +21788,7 @@
     <row r="393">
       <c r="A393" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B393" s="9" t="inlineStr">
@@ -21830,7 +21830,7 @@
     <row r="394">
       <c r="A394" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B394" s="9" t="inlineStr">
@@ -21872,7 +21872,7 @@
     <row r="395">
       <c r="A395" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B395" s="9" t="inlineStr">
@@ -21914,7 +21914,7 @@
     <row r="396">
       <c r="A396" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B396" s="9" t="inlineStr">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="G396" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="H396" s="9" t="inlineStr">
@@ -21956,7 +21956,7 @@
     <row r="397">
       <c r="A397" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B397" s="9" t="inlineStr">
@@ -21998,7 +21998,7 @@
     <row r="398">
       <c r="A398" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B398" s="9" t="inlineStr">
@@ -22040,7 +22040,7 @@
     <row r="399">
       <c r="A399" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B399" s="9" t="inlineStr">
@@ -22082,7 +22082,7 @@
     <row r="400">
       <c r="A400" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B400" s="9" t="inlineStr">
@@ -22124,7 +22124,7 @@
     <row r="401">
       <c r="A401" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B401" s="9" t="inlineStr">
@@ -22166,7 +22166,7 @@
     <row r="402">
       <c r="A402" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B402" s="9" t="inlineStr">
@@ -22208,7 +22208,7 @@
     <row r="403">
       <c r="A403" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B403" s="9" t="inlineStr">
@@ -22250,7 +22250,7 @@
     <row r="404">
       <c r="A404" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B404" s="9" t="inlineStr">
@@ -22280,7 +22280,7 @@
       </c>
       <c r="G404" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H404" s="9" t="inlineStr">
@@ -22292,7 +22292,7 @@
     <row r="405">
       <c r="A405" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B405" s="9" t="inlineStr">
@@ -22334,7 +22334,7 @@
     <row r="406">
       <c r="A406" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B406" s="9" t="inlineStr">
@@ -22376,7 +22376,7 @@
     <row r="407">
       <c r="A407" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B407" s="9" t="inlineStr">
@@ -22418,7 +22418,7 @@
     <row r="408">
       <c r="A408" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B408" s="9" t="inlineStr">
@@ -22438,17 +22438,17 @@
       </c>
       <c r="E408" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F408" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G408" s="9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H408" s="9" t="inlineStr">
@@ -22460,7 +22460,7 @@
     <row r="409">
       <c r="A409" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B409" s="9" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="G409" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H409" s="9" t="inlineStr">
@@ -22502,7 +22502,7 @@
     <row r="410">
       <c r="A410" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B410" s="9" t="inlineStr">
@@ -22544,7 +22544,7 @@
     <row r="411">
       <c r="A411" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B411" s="9" t="inlineStr">
@@ -22586,7 +22586,7 @@
     <row r="412">
       <c r="A412" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B412" s="9" t="inlineStr">
@@ -22628,7 +22628,7 @@
     <row r="413">
       <c r="A413" s="9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B413" s="9" t="inlineStr">
@@ -22670,7 +22670,7 @@
     <row r="414">
       <c r="A414" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B414" s="9" t="inlineStr">
@@ -22712,7 +22712,7 @@
     <row r="415">
       <c r="A415" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B415" s="9" t="inlineStr">
@@ -22754,7 +22754,7 @@
     <row r="416">
       <c r="A416" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B416" s="9" t="inlineStr">
@@ -22796,7 +22796,7 @@
     <row r="417">
       <c r="A417" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B417" s="9" t="inlineStr">
@@ -22838,7 +22838,7 @@
     <row r="418">
       <c r="A418" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B418" s="9" t="inlineStr">
@@ -22880,7 +22880,7 @@
     <row r="419">
       <c r="A419" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B419" s="9" t="inlineStr">
@@ -22922,7 +22922,7 @@
     <row r="420">
       <c r="A420" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B420" s="9" t="inlineStr">
@@ -22964,7 +22964,7 @@
     <row r="421">
       <c r="A421" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B421" s="9" t="inlineStr">
@@ -23006,7 +23006,7 @@
     <row r="422">
       <c r="A422" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B422" s="9" t="inlineStr">
@@ -23048,7 +23048,7 @@
     <row r="423">
       <c r="A423" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B423" s="9" t="inlineStr">
@@ -23090,7 +23090,7 @@
     <row r="424">
       <c r="A424" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B424" s="9" t="inlineStr">
@@ -23132,7 +23132,7 @@
     <row r="425">
       <c r="A425" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B425" s="9" t="inlineStr">
@@ -23174,7 +23174,7 @@
     <row r="426">
       <c r="A426" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B426" s="9" t="inlineStr">
@@ -23216,7 +23216,7 @@
     <row r="427">
       <c r="A427" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B427" s="9" t="inlineStr">
@@ -23258,7 +23258,7 @@
     <row r="428">
       <c r="A428" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B428" s="9" t="inlineStr">
@@ -23300,7 +23300,7 @@
     <row r="429">
       <c r="A429" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B429" s="9" t="inlineStr">
@@ -23342,7 +23342,7 @@
     <row r="430">
       <c r="A430" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B430" s="9" t="inlineStr">
@@ -23384,7 +23384,7 @@
     <row r="431">
       <c r="A431" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B431" s="9" t="inlineStr">
@@ -23426,7 +23426,7 @@
     <row r="432">
       <c r="A432" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B432" s="9" t="inlineStr">
@@ -23468,7 +23468,7 @@
     <row r="433">
       <c r="A433" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B433" s="9" t="inlineStr">
@@ -23510,7 +23510,7 @@
     <row r="434">
       <c r="A434" s="9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B434" s="9" t="inlineStr">
@@ -23552,7 +23552,7 @@
     <row r="435">
       <c r="A435" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B435" s="9" t="inlineStr">
@@ -23594,7 +23594,7 @@
     <row r="436">
       <c r="A436" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B436" s="9" t="inlineStr">
@@ -23636,7 +23636,7 @@
     <row r="437">
       <c r="A437" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B437" s="9" t="inlineStr">
@@ -23678,7 +23678,7 @@
     <row r="438">
       <c r="A438" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B438" s="9" t="inlineStr">
@@ -23720,7 +23720,7 @@
     <row r="439">
       <c r="A439" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B439" s="9" t="inlineStr">
@@ -23762,7 +23762,7 @@
     <row r="440">
       <c r="A440" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B440" s="9" t="inlineStr">
@@ -23804,7 +23804,7 @@
     <row r="441">
       <c r="A441" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B441" s="9" t="inlineStr">
@@ -23846,7 +23846,7 @@
     <row r="442">
       <c r="A442" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B442" s="9" t="inlineStr">
@@ -23888,7 +23888,7 @@
     <row r="443">
       <c r="A443" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B443" s="9" t="inlineStr">
@@ -23930,7 +23930,7 @@
     <row r="444">
       <c r="A444" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B444" s="9" t="inlineStr">
@@ -23972,7 +23972,7 @@
     <row r="445">
       <c r="A445" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B445" s="9" t="inlineStr">
@@ -24014,7 +24014,7 @@
     <row r="446">
       <c r="A446" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B446" s="9" t="inlineStr">
@@ -24056,7 +24056,7 @@
     <row r="447">
       <c r="A447" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B447" s="9" t="inlineStr">
@@ -24098,7 +24098,7 @@
     <row r="448">
       <c r="A448" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B448" s="9" t="inlineStr">
@@ -24140,7 +24140,7 @@
     <row r="449">
       <c r="A449" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B449" s="9" t="inlineStr">
@@ -24182,7 +24182,7 @@
     <row r="450">
       <c r="A450" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B450" s="9" t="inlineStr">
@@ -24224,7 +24224,7 @@
     <row r="451">
       <c r="A451" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B451" s="9" t="inlineStr">
@@ -24266,7 +24266,7 @@
     <row r="452">
       <c r="A452" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B452" s="9" t="inlineStr">
@@ -24308,7 +24308,7 @@
     <row r="453">
       <c r="A453" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B453" s="9" t="inlineStr">
@@ -24350,7 +24350,7 @@
     <row r="454">
       <c r="A454" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B454" s="9" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="455">
       <c r="A455" s="9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B455" s="9" t="inlineStr">
@@ -24434,7 +24434,7 @@
     <row r="456">
       <c r="A456" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B456" s="9" t="inlineStr">
@@ -24476,7 +24476,7 @@
     <row r="457">
       <c r="A457" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B457" s="9" t="inlineStr">
@@ -24518,7 +24518,7 @@
     <row r="458">
       <c r="A458" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B458" s="9" t="inlineStr">
@@ -24560,7 +24560,7 @@
     <row r="459">
       <c r="A459" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B459" s="9" t="inlineStr">
@@ -24602,7 +24602,7 @@
     <row r="460">
       <c r="A460" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B460" s="9" t="inlineStr">
@@ -24644,7 +24644,7 @@
     <row r="461">
       <c r="A461" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B461" s="9" t="inlineStr">
@@ -24686,7 +24686,7 @@
     <row r="462">
       <c r="A462" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B462" s="9" t="inlineStr">
@@ -24728,7 +24728,7 @@
     <row r="463">
       <c r="A463" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B463" s="9" t="inlineStr">
@@ -24770,7 +24770,7 @@
     <row r="464">
       <c r="A464" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B464" s="9" t="inlineStr">
@@ -24812,7 +24812,7 @@
     <row r="465">
       <c r="A465" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B465" s="9" t="inlineStr">
@@ -24854,7 +24854,7 @@
     <row r="466">
       <c r="A466" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B466" s="9" t="inlineStr">
@@ -24896,7 +24896,7 @@
     <row r="467">
       <c r="A467" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B467" s="9" t="inlineStr">
@@ -24926,7 +24926,7 @@
       </c>
       <c r="G467" s="9" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="H467" s="9" t="inlineStr">
@@ -24938,7 +24938,7 @@
     <row r="468">
       <c r="A468" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B468" s="9" t="inlineStr">
@@ -24980,7 +24980,7 @@
     <row r="469">
       <c r="A469" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B469" s="9" t="inlineStr">
@@ -25022,7 +25022,7 @@
     <row r="470">
       <c r="A470" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B470" s="9" t="inlineStr">
@@ -25064,7 +25064,7 @@
     <row r="471">
       <c r="A471" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B471" s="9" t="inlineStr">
@@ -25106,7 +25106,7 @@
     <row r="472">
       <c r="A472" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B472" s="9" t="inlineStr">
@@ -25148,7 +25148,7 @@
     <row r="473">
       <c r="A473" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B473" s="9" t="inlineStr">
@@ -25190,7 +25190,7 @@
     <row r="474">
       <c r="A474" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B474" s="9" t="inlineStr">
@@ -25232,7 +25232,7 @@
     <row r="475">
       <c r="A475" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B475" s="9" t="inlineStr">
@@ -25274,7 +25274,7 @@
     <row r="476">
       <c r="A476" s="9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B476" s="9" t="inlineStr">
@@ -25316,7 +25316,7 @@
     <row r="477">
       <c r="A477" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B477" s="9" t="inlineStr">
@@ -25358,7 +25358,7 @@
     <row r="478">
       <c r="A478" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B478" s="9" t="inlineStr">
@@ -25400,7 +25400,7 @@
     <row r="479">
       <c r="A479" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B479" s="9" t="inlineStr">
@@ -25442,7 +25442,7 @@
     <row r="480">
       <c r="A480" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B480" s="9" t="inlineStr">
@@ -25484,7 +25484,7 @@
     <row r="481">
       <c r="A481" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B481" s="9" t="inlineStr">
@@ -25526,7 +25526,7 @@
     <row r="482">
       <c r="A482" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B482" s="9" t="inlineStr">
@@ -25568,7 +25568,7 @@
     <row r="483">
       <c r="A483" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B483" s="9" t="inlineStr">
@@ -25610,7 +25610,7 @@
     <row r="484">
       <c r="A484" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B484" s="9" t="inlineStr">
@@ -25652,7 +25652,7 @@
     <row r="485">
       <c r="A485" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B485" s="9" t="inlineStr">
@@ -25694,7 +25694,7 @@
     <row r="486">
       <c r="A486" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B486" s="9" t="inlineStr">
@@ -25736,7 +25736,7 @@
     <row r="487">
       <c r="A487" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B487" s="9" t="inlineStr">
@@ -25778,7 +25778,7 @@
     <row r="488">
       <c r="A488" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B488" s="9" t="inlineStr">
@@ -25808,7 +25808,7 @@
       </c>
       <c r="G488" s="9" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="H488" s="9" t="inlineStr">
@@ -25820,7 +25820,7 @@
     <row r="489">
       <c r="A489" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B489" s="9" t="inlineStr">
@@ -25862,7 +25862,7 @@
     <row r="490">
       <c r="A490" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B490" s="9" t="inlineStr">
@@ -25904,7 +25904,7 @@
     <row r="491">
       <c r="A491" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B491" s="9" t="inlineStr">
@@ -25946,7 +25946,7 @@
     <row r="492">
       <c r="A492" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B492" s="9" t="inlineStr">
@@ -25988,7 +25988,7 @@
     <row r="493">
       <c r="A493" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B493" s="9" t="inlineStr">
@@ -26030,7 +26030,7 @@
     <row r="494">
       <c r="A494" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B494" s="9" t="inlineStr">
@@ -26072,7 +26072,7 @@
     <row r="495">
       <c r="A495" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B495" s="9" t="inlineStr">
@@ -26114,7 +26114,7 @@
     <row r="496">
       <c r="A496" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B496" s="9" t="inlineStr">
@@ -26156,7 +26156,7 @@
     <row r="497">
       <c r="A497" s="9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B497" s="9" t="inlineStr">
@@ -26198,7 +26198,7 @@
     <row r="498">
       <c r="A498" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B498" s="9" t="inlineStr">
@@ -26240,7 +26240,7 @@
     <row r="499">
       <c r="A499" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B499" s="9" t="inlineStr">
@@ -26282,7 +26282,7 @@
     <row r="500">
       <c r="A500" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B500" s="9" t="inlineStr">
@@ -26324,7 +26324,7 @@
     <row r="501">
       <c r="A501" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B501" s="9" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="G501" s="9" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H501" s="9" t="inlineStr">
@@ -26366,7 +26366,7 @@
     <row r="502">
       <c r="A502" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B502" s="9" t="inlineStr">
@@ -26408,7 +26408,7 @@
     <row r="503">
       <c r="A503" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B503" s="9" t="inlineStr">
@@ -26450,7 +26450,7 @@
     <row r="504">
       <c r="A504" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B504" s="9" t="inlineStr">
@@ -26492,7 +26492,7 @@
     <row r="505">
       <c r="A505" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B505" s="9" t="inlineStr">
@@ -26534,7 +26534,7 @@
     <row r="506">
       <c r="A506" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B506" s="9" t="inlineStr">
@@ -26576,7 +26576,7 @@
     <row r="507">
       <c r="A507" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B507" s="9" t="inlineStr">
@@ -26618,7 +26618,7 @@
     <row r="508">
       <c r="A508" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B508" s="9" t="inlineStr">
@@ -26660,7 +26660,7 @@
     <row r="509">
       <c r="A509" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B509" s="9" t="inlineStr">
@@ -26702,7 +26702,7 @@
     <row r="510">
       <c r="A510" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B510" s="9" t="inlineStr">
@@ -26744,7 +26744,7 @@
     <row r="511">
       <c r="A511" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B511" s="9" t="inlineStr">
@@ -26786,7 +26786,7 @@
     <row r="512">
       <c r="A512" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B512" s="9" t="inlineStr">
@@ -26828,7 +26828,7 @@
     <row r="513">
       <c r="A513" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B513" s="9" t="inlineStr">
@@ -26870,7 +26870,7 @@
     <row r="514">
       <c r="A514" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B514" s="9" t="inlineStr">
@@ -26900,7 +26900,7 @@
       </c>
       <c r="G514" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H514" s="9" t="inlineStr">
@@ -26912,7 +26912,7 @@
     <row r="515">
       <c r="A515" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B515" s="9" t="inlineStr">
@@ -26932,17 +26932,17 @@
       </c>
       <c r="E515" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F515" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G515" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H515" s="9" t="inlineStr">
@@ -26954,7 +26954,7 @@
     <row r="516">
       <c r="A516" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B516" s="9" t="inlineStr">
@@ -26996,7 +26996,7 @@
     <row r="517">
       <c r="A517" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B517" s="9" t="inlineStr">
@@ -27026,7 +27026,7 @@
       </c>
       <c r="G517" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H517" s="9" t="inlineStr">
@@ -27038,7 +27038,7 @@
     <row r="518">
       <c r="A518" s="9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B518" s="9" t="inlineStr">
@@ -27080,7 +27080,7 @@
     <row r="519">
       <c r="A519" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B519" s="9" t="inlineStr">
@@ -27122,7 +27122,7 @@
     <row r="520">
       <c r="A520" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B520" s="9" t="inlineStr">
@@ -27164,7 +27164,7 @@
     <row r="521">
       <c r="A521" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B521" s="9" t="inlineStr">
@@ -27206,7 +27206,7 @@
     <row r="522">
       <c r="A522" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B522" s="9" t="inlineStr">
@@ -27248,7 +27248,7 @@
     <row r="523">
       <c r="A523" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B523" s="9" t="inlineStr">
@@ -27290,7 +27290,7 @@
     <row r="524">
       <c r="A524" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B524" s="9" t="inlineStr">
@@ -27332,7 +27332,7 @@
     <row r="525">
       <c r="A525" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B525" s="9" t="inlineStr">
@@ -27374,7 +27374,7 @@
     <row r="526">
       <c r="A526" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B526" s="9" t="inlineStr">
@@ -27416,7 +27416,7 @@
     <row r="527">
       <c r="A527" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B527" s="9" t="inlineStr">
@@ -27458,7 +27458,7 @@
     <row r="528">
       <c r="A528" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B528" s="9" t="inlineStr">
@@ -27500,7 +27500,7 @@
     <row r="529">
       <c r="A529" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B529" s="9" t="inlineStr">
@@ -27542,7 +27542,7 @@
     <row r="530">
       <c r="A530" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B530" s="9" t="inlineStr">
@@ -27584,7 +27584,7 @@
     <row r="531">
       <c r="A531" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B531" s="9" t="inlineStr">
@@ -27626,7 +27626,7 @@
     <row r="532">
       <c r="A532" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B532" s="9" t="inlineStr">
@@ -27668,7 +27668,7 @@
     <row r="533">
       <c r="A533" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B533" s="9" t="inlineStr">
@@ -27710,7 +27710,7 @@
     <row r="534">
       <c r="A534" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B534" s="9" t="inlineStr">
@@ -27752,7 +27752,7 @@
     <row r="535">
       <c r="A535" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B535" s="9" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="536">
       <c r="A536" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B536" s="9" t="inlineStr">
@@ -27836,7 +27836,7 @@
     <row r="537">
       <c r="A537" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B537" s="9" t="inlineStr">
@@ -27878,7 +27878,7 @@
     <row r="538">
       <c r="A538" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B538" s="9" t="inlineStr">
@@ -27920,7 +27920,7 @@
     <row r="539">
       <c r="A539" s="9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B539" s="9" t="inlineStr">
@@ -27962,7 +27962,7 @@
     <row r="540">
       <c r="A540" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B540" s="9" t="inlineStr">
@@ -28004,7 +28004,7 @@
     <row r="541">
       <c r="A541" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B541" s="9" t="inlineStr">
@@ -28046,7 +28046,7 @@
     <row r="542">
       <c r="A542" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B542" s="9" t="inlineStr">
@@ -28088,7 +28088,7 @@
     <row r="543">
       <c r="A543" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B543" s="9" t="inlineStr">
@@ -28130,7 +28130,7 @@
     <row r="544">
       <c r="A544" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B544" s="9" t="inlineStr">
@@ -28172,7 +28172,7 @@
     <row r="545">
       <c r="A545" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B545" s="9" t="inlineStr">
@@ -28214,7 +28214,7 @@
     <row r="546">
       <c r="A546" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B546" s="9" t="inlineStr">
@@ -28256,7 +28256,7 @@
     <row r="547">
       <c r="A547" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B547" s="9" t="inlineStr">
@@ -28298,7 +28298,7 @@
     <row r="548">
       <c r="A548" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B548" s="9" t="inlineStr">
@@ -28340,7 +28340,7 @@
     <row r="549">
       <c r="A549" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B549" s="9" t="inlineStr">
@@ -28382,7 +28382,7 @@
     <row r="550">
       <c r="A550" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B550" s="9" t="inlineStr">
@@ -28424,7 +28424,7 @@
     <row r="551">
       <c r="A551" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B551" s="9" t="inlineStr">
@@ -28466,7 +28466,7 @@
     <row r="552">
       <c r="A552" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B552" s="9" t="inlineStr">
@@ -28508,7 +28508,7 @@
     <row r="553">
       <c r="A553" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B553" s="9" t="inlineStr">
@@ -28550,7 +28550,7 @@
     <row r="554">
       <c r="A554" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B554" s="9" t="inlineStr">
@@ -28592,7 +28592,7 @@
     <row r="555">
       <c r="A555" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B555" s="9" t="inlineStr">
@@ -28634,7 +28634,7 @@
     <row r="556">
       <c r="A556" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B556" s="9" t="inlineStr">
@@ -28676,7 +28676,7 @@
     <row r="557">
       <c r="A557" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B557" s="9" t="inlineStr">
@@ -28718,7 +28718,7 @@
     <row r="558">
       <c r="A558" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B558" s="9" t="inlineStr">
@@ -28760,7 +28760,7 @@
     <row r="559">
       <c r="A559" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B559" s="9" t="inlineStr">
@@ -28802,7 +28802,7 @@
     <row r="560">
       <c r="A560" s="9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B560" s="9" t="inlineStr">
@@ -28844,7 +28844,7 @@
     <row r="561">
       <c r="A561" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B561" s="9" t="inlineStr">
@@ -28886,7 +28886,7 @@
     <row r="562">
       <c r="A562" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B562" s="9" t="inlineStr">
@@ -28928,7 +28928,7 @@
     <row r="563">
       <c r="A563" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B563" s="9" t="inlineStr">
@@ -28970,7 +28970,7 @@
     <row r="564">
       <c r="A564" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B564" s="9" t="inlineStr">
@@ -29012,7 +29012,7 @@
     <row r="565">
       <c r="A565" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B565" s="9" t="inlineStr">
@@ -29054,7 +29054,7 @@
     <row r="566">
       <c r="A566" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B566" s="9" t="inlineStr">
@@ -29096,7 +29096,7 @@
     <row r="567">
       <c r="A567" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B567" s="9" t="inlineStr">
@@ -29138,7 +29138,7 @@
     <row r="568">
       <c r="A568" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B568" s="9" t="inlineStr">
@@ -29180,7 +29180,7 @@
     <row r="569">
       <c r="A569" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B569" s="9" t="inlineStr">
@@ -29222,7 +29222,7 @@
     <row r="570">
       <c r="A570" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B570" s="9" t="inlineStr">
@@ -29264,7 +29264,7 @@
     <row r="571">
       <c r="A571" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B571" s="9" t="inlineStr">
@@ -29306,7 +29306,7 @@
     <row r="572">
       <c r="A572" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B572" s="9" t="inlineStr">
@@ -29348,7 +29348,7 @@
     <row r="573">
       <c r="A573" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B573" s="9" t="inlineStr">
@@ -29390,7 +29390,7 @@
     <row r="574">
       <c r="A574" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B574" s="9" t="inlineStr">
@@ -29432,7 +29432,7 @@
     <row r="575">
       <c r="A575" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B575" s="9" t="inlineStr">
@@ -29474,7 +29474,7 @@
     <row r="576">
       <c r="A576" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B576" s="9" t="inlineStr">
@@ -29516,7 +29516,7 @@
     <row r="577">
       <c r="A577" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B577" s="9" t="inlineStr">
@@ -29558,7 +29558,7 @@
     <row r="578">
       <c r="A578" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B578" s="9" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="579">
       <c r="A579" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B579" s="9" t="inlineStr">
@@ -29642,7 +29642,7 @@
     <row r="580">
       <c r="A580" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B580" s="9" t="inlineStr">
@@ -29684,7 +29684,7 @@
     <row r="581">
       <c r="A581" s="9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B581" s="9" t="inlineStr">
@@ -29726,7 +29726,7 @@
     <row r="582">
       <c r="A582" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B582" s="9" t="inlineStr">
@@ -29768,7 +29768,7 @@
     <row r="583">
       <c r="A583" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B583" s="9" t="inlineStr">
@@ -29810,7 +29810,7 @@
     <row r="584">
       <c r="A584" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B584" s="9" t="inlineStr">
@@ -29852,7 +29852,7 @@
     <row r="585">
       <c r="A585" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B585" s="9" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="586">
       <c r="A586" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B586" s="9" t="inlineStr">
@@ -29936,7 +29936,7 @@
     <row r="587">
       <c r="A587" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B587" s="9" t="inlineStr">
@@ -29978,7 +29978,7 @@
     <row r="588">
       <c r="A588" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B588" s="9" t="inlineStr">
@@ -30020,7 +30020,7 @@
     <row r="589">
       <c r="A589" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B589" s="9" t="inlineStr">
@@ -30062,7 +30062,7 @@
     <row r="590">
       <c r="A590" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B590" s="9" t="inlineStr">
@@ -30104,7 +30104,7 @@
     <row r="591">
       <c r="A591" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B591" s="9" t="inlineStr">
@@ -30146,7 +30146,7 @@
     <row r="592">
       <c r="A592" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B592" s="9" t="inlineStr">
@@ -30188,7 +30188,7 @@
     <row r="593">
       <c r="A593" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B593" s="9" t="inlineStr">
@@ -30230,7 +30230,7 @@
     <row r="594">
       <c r="A594" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B594" s="9" t="inlineStr">
@@ -30272,7 +30272,7 @@
     <row r="595">
       <c r="A595" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B595" s="9" t="inlineStr">
@@ -30314,7 +30314,7 @@
     <row r="596">
       <c r="A596" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B596" s="9" t="inlineStr">
@@ -30356,7 +30356,7 @@
     <row r="597">
       <c r="A597" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B597" s="9" t="inlineStr">
@@ -30398,7 +30398,7 @@
     <row r="598">
       <c r="A598" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B598" s="9" t="inlineStr">
@@ -30440,7 +30440,7 @@
     <row r="599">
       <c r="A599" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B599" s="9" t="inlineStr">
@@ -30482,7 +30482,7 @@
     <row r="600">
       <c r="A600" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B600" s="9" t="inlineStr">
@@ -30524,7 +30524,7 @@
     <row r="601">
       <c r="A601" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B601" s="9" t="inlineStr">
@@ -30566,7 +30566,7 @@
     <row r="602">
       <c r="A602" s="9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B602" s="9" t="inlineStr">
@@ -30608,7 +30608,7 @@
     <row r="603">
       <c r="A603" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B603" s="9" t="inlineStr">
@@ -30650,7 +30650,7 @@
     <row r="604">
       <c r="A604" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B604" s="9" t="inlineStr">
@@ -30692,7 +30692,7 @@
     <row r="605">
       <c r="A605" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B605" s="9" t="inlineStr">
@@ -30734,7 +30734,7 @@
     <row r="606">
       <c r="A606" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B606" s="9" t="inlineStr">
@@ -30776,7 +30776,7 @@
     <row r="607">
       <c r="A607" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B607" s="9" t="inlineStr">
@@ -30818,7 +30818,7 @@
     <row r="608">
       <c r="A608" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B608" s="9" t="inlineStr">
@@ -30860,7 +30860,7 @@
     <row r="609">
       <c r="A609" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B609" s="9" t="inlineStr">
@@ -30902,7 +30902,7 @@
     <row r="610">
       <c r="A610" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B610" s="9" t="inlineStr">
@@ -30944,7 +30944,7 @@
     <row r="611">
       <c r="A611" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B611" s="9" t="inlineStr">
@@ -30964,17 +30964,17 @@
       </c>
       <c r="E611" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F611" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G611" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H611" s="9" t="inlineStr">
@@ -30986,7 +30986,7 @@
     <row r="612">
       <c r="A612" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B612" s="9" t="inlineStr">
@@ -31028,7 +31028,7 @@
     <row r="613">
       <c r="A613" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B613" s="9" t="inlineStr">
@@ -31070,7 +31070,7 @@
     <row r="614">
       <c r="A614" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B614" s="9" t="inlineStr">
@@ -31112,7 +31112,7 @@
     <row r="615">
       <c r="A615" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B615" s="9" t="inlineStr">
@@ -31154,7 +31154,7 @@
     <row r="616">
       <c r="A616" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B616" s="9" t="inlineStr">
@@ -31196,7 +31196,7 @@
     <row r="617">
       <c r="A617" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B617" s="9" t="inlineStr">
@@ -31216,17 +31216,17 @@
       </c>
       <c r="E617" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F617" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G617" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H617" s="9" t="inlineStr">
@@ -31238,7 +31238,7 @@
     <row r="618">
       <c r="A618" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B618" s="9" t="inlineStr">
@@ -31280,7 +31280,7 @@
     <row r="619">
       <c r="A619" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B619" s="9" t="inlineStr">
@@ -31310,7 +31310,7 @@
       </c>
       <c r="G619" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H619" s="9" t="inlineStr">
@@ -31322,7 +31322,7 @@
     <row r="620">
       <c r="A620" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B620" s="9" t="inlineStr">
@@ -31342,17 +31342,17 @@
       </c>
       <c r="E620" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F620" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G620" s="9" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="H620" s="9" t="inlineStr">
@@ -31364,7 +31364,7 @@
     <row r="621">
       <c r="A621" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B621" s="9" t="inlineStr">
@@ -31406,7 +31406,7 @@
     <row r="622">
       <c r="A622" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B622" s="9" t="inlineStr">
@@ -31426,7 +31426,7 @@
       </c>
       <c r="E622" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F622" s="9" t="inlineStr">
@@ -31436,7 +31436,7 @@
       </c>
       <c r="G622" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="H622" s="9" t="inlineStr">
@@ -31448,7 +31448,7 @@
     <row r="623">
       <c r="A623" s="9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B623" s="9" t="inlineStr">
@@ -31490,7 +31490,7 @@
     <row r="624">
       <c r="A624" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B624" s="9" t="inlineStr">
@@ -31532,7 +31532,7 @@
     <row r="625">
       <c r="A625" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B625" s="9" t="inlineStr">
@@ -31574,7 +31574,7 @@
     <row r="626">
       <c r="A626" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B626" s="9" t="inlineStr">
@@ -31616,7 +31616,7 @@
     <row r="627">
       <c r="A627" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B627" s="9" t="inlineStr">
@@ -31658,7 +31658,7 @@
     <row r="628">
       <c r="A628" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B628" s="9" t="inlineStr">
@@ -31700,7 +31700,7 @@
     <row r="629">
       <c r="A629" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B629" s="9" t="inlineStr">
@@ -31742,7 +31742,7 @@
     <row r="630">
       <c r="A630" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B630" s="9" t="inlineStr">
@@ -31784,7 +31784,7 @@
     <row r="631">
       <c r="A631" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B631" s="9" t="inlineStr">
@@ -31826,7 +31826,7 @@
     <row r="632">
       <c r="A632" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B632" s="9" t="inlineStr">
@@ -31868,7 +31868,7 @@
     <row r="633">
       <c r="A633" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B633" s="9" t="inlineStr">
@@ -31910,7 +31910,7 @@
     <row r="634">
       <c r="A634" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B634" s="9" t="inlineStr">
@@ -31952,7 +31952,7 @@
     <row r="635">
       <c r="A635" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B635" s="9" t="inlineStr">
@@ -31994,7 +31994,7 @@
     <row r="636">
       <c r="A636" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B636" s="9" t="inlineStr">
@@ -32036,7 +32036,7 @@
     <row r="637">
       <c r="A637" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B637" s="9" t="inlineStr">
@@ -32078,7 +32078,7 @@
     <row r="638">
       <c r="A638" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B638" s="9" t="inlineStr">
@@ -32120,7 +32120,7 @@
     <row r="639">
       <c r="A639" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B639" s="9" t="inlineStr">
@@ -32162,7 +32162,7 @@
     <row r="640">
       <c r="A640" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B640" s="9" t="inlineStr">
@@ -32204,7 +32204,7 @@
     <row r="641">
       <c r="A641" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B641" s="9" t="inlineStr">
@@ -32246,7 +32246,7 @@
     <row r="642">
       <c r="A642" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B642" s="9" t="inlineStr">
@@ -32288,7 +32288,7 @@
     <row r="643">
       <c r="A643" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B643" s="9" t="inlineStr">
@@ -32330,7 +32330,7 @@
     <row r="644">
       <c r="A644" s="9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B644" s="9" t="inlineStr">
@@ -32372,7 +32372,7 @@
     <row r="645">
       <c r="A645" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B645" s="9" t="inlineStr">
@@ -32414,7 +32414,7 @@
     <row r="646">
       <c r="A646" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B646" s="9" t="inlineStr">
@@ -32456,7 +32456,7 @@
     <row r="647">
       <c r="A647" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B647" s="9" t="inlineStr">
@@ -32498,7 +32498,7 @@
     <row r="648">
       <c r="A648" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B648" s="9" t="inlineStr">
@@ -32540,7 +32540,7 @@
     <row r="649">
       <c r="A649" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B649" s="9" t="inlineStr">
@@ -32582,7 +32582,7 @@
     <row r="650">
       <c r="A650" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B650" s="9" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="651">
       <c r="A651" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B651" s="9" t="inlineStr">
@@ -32666,7 +32666,7 @@
     <row r="652">
       <c r="A652" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B652" s="9" t="inlineStr">
@@ -32708,7 +32708,7 @@
     <row r="653">
       <c r="A653" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B653" s="9" t="inlineStr">
@@ -32750,7 +32750,7 @@
     <row r="654">
       <c r="A654" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B654" s="9" t="inlineStr">
@@ -32792,7 +32792,7 @@
     <row r="655">
       <c r="A655" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B655" s="9" t="inlineStr">
@@ -32834,7 +32834,7 @@
     <row r="656">
       <c r="A656" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B656" s="9" t="inlineStr">
@@ -32876,7 +32876,7 @@
     <row r="657">
       <c r="A657" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B657" s="9" t="inlineStr">
@@ -32918,7 +32918,7 @@
     <row r="658">
       <c r="A658" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B658" s="9" t="inlineStr">
@@ -32960,7 +32960,7 @@
     <row r="659">
       <c r="A659" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B659" s="9" t="inlineStr">
@@ -33002,7 +33002,7 @@
     <row r="660">
       <c r="A660" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B660" s="9" t="inlineStr">
@@ -33044,7 +33044,7 @@
     <row r="661">
       <c r="A661" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B661" s="9" t="inlineStr">
@@ -33086,7 +33086,7 @@
     <row r="662">
       <c r="A662" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B662" s="9" t="inlineStr">
@@ -33128,7 +33128,7 @@
     <row r="663">
       <c r="A663" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B663" s="9" t="inlineStr">
@@ -33170,7 +33170,7 @@
     <row r="664">
       <c r="A664" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B664" s="9" t="inlineStr">
@@ -33212,7 +33212,7 @@
     <row r="665">
       <c r="A665" s="9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B665" s="9" t="inlineStr">
@@ -33254,7 +33254,7 @@
     <row r="666">
       <c r="A666" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B666" s="9" t="inlineStr">
@@ -33296,7 +33296,7 @@
     <row r="667">
       <c r="A667" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B667" s="9" t="inlineStr">
@@ -33338,7 +33338,7 @@
     <row r="668">
       <c r="A668" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B668" s="9" t="inlineStr">
@@ -33380,7 +33380,7 @@
     <row r="669">
       <c r="A669" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B669" s="9" t="inlineStr">
@@ -33422,7 +33422,7 @@
     <row r="670">
       <c r="A670" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B670" s="9" t="inlineStr">
@@ -33464,7 +33464,7 @@
     <row r="671">
       <c r="A671" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B671" s="9" t="inlineStr">
@@ -33506,7 +33506,7 @@
     <row r="672">
       <c r="A672" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B672" s="9" t="inlineStr">
@@ -33548,7 +33548,7 @@
     <row r="673">
       <c r="A673" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B673" s="9" t="inlineStr">
@@ -33590,7 +33590,7 @@
     <row r="674">
       <c r="A674" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B674" s="9" t="inlineStr">
@@ -33632,7 +33632,7 @@
     <row r="675">
       <c r="A675" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B675" s="9" t="inlineStr">
@@ -33674,7 +33674,7 @@
     <row r="676">
       <c r="A676" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B676" s="9" t="inlineStr">
@@ -33716,7 +33716,7 @@
     <row r="677">
       <c r="A677" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B677" s="9" t="inlineStr">
@@ -33758,7 +33758,7 @@
     <row r="678">
       <c r="A678" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B678" s="9" t="inlineStr">
@@ -33800,7 +33800,7 @@
     <row r="679">
       <c r="A679" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B679" s="9" t="inlineStr">
@@ -33842,7 +33842,7 @@
     <row r="680">
       <c r="A680" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B680" s="9" t="inlineStr">
@@ -33884,7 +33884,7 @@
     <row r="681">
       <c r="A681" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B681" s="9" t="inlineStr">
@@ -33926,7 +33926,7 @@
     <row r="682">
       <c r="A682" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B682" s="9" t="inlineStr">
@@ -33968,7 +33968,7 @@
     <row r="683">
       <c r="A683" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B683" s="9" t="inlineStr">
@@ -34010,7 +34010,7 @@
     <row r="684">
       <c r="A684" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B684" s="9" t="inlineStr">
@@ -34052,7 +34052,7 @@
     <row r="685">
       <c r="A685" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B685" s="9" t="inlineStr">
@@ -34094,7 +34094,7 @@
     <row r="686">
       <c r="A686" s="9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B686" s="9" t="inlineStr">
@@ -34136,7 +34136,7 @@
     <row r="687">
       <c r="A687" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B687" s="9" t="inlineStr">
@@ -34178,7 +34178,7 @@
     <row r="688">
       <c r="A688" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B688" s="9" t="inlineStr">
@@ -34220,7 +34220,7 @@
     <row r="689">
       <c r="A689" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B689" s="9" t="inlineStr">
@@ -34262,7 +34262,7 @@
     <row r="690">
       <c r="A690" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B690" s="9" t="inlineStr">
@@ -34304,7 +34304,7 @@
     <row r="691">
       <c r="A691" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B691" s="9" t="inlineStr">
@@ -34346,7 +34346,7 @@
     <row r="692">
       <c r="A692" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B692" s="9" t="inlineStr">
@@ -34388,7 +34388,7 @@
     <row r="693">
       <c r="A693" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B693" s="9" t="inlineStr">
@@ -34430,7 +34430,7 @@
     <row r="694">
       <c r="A694" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B694" s="9" t="inlineStr">
@@ -34472,7 +34472,7 @@
     <row r="695">
       <c r="A695" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B695" s="9" t="inlineStr">
@@ -34514,7 +34514,7 @@
     <row r="696">
       <c r="A696" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B696" s="9" t="inlineStr">
@@ -34556,7 +34556,7 @@
     <row r="697">
       <c r="A697" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B697" s="9" t="inlineStr">
@@ -34598,7 +34598,7 @@
     <row r="698">
       <c r="A698" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B698" s="9" t="inlineStr">
@@ -34640,7 +34640,7 @@
     <row r="699">
       <c r="A699" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B699" s="9" t="inlineStr">
@@ -34682,7 +34682,7 @@
     <row r="700">
       <c r="A700" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B700" s="9" t="inlineStr">
@@ -34724,7 +34724,7 @@
     <row r="701">
       <c r="A701" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B701" s="9" t="inlineStr">
@@ -34766,7 +34766,7 @@
     <row r="702">
       <c r="A702" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B702" s="9" t="inlineStr">
@@ -34808,7 +34808,7 @@
     <row r="703">
       <c r="A703" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B703" s="9" t="inlineStr">
@@ -34850,7 +34850,7 @@
     <row r="704">
       <c r="A704" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B704" s="9" t="inlineStr">
@@ -34892,7 +34892,7 @@
     <row r="705">
       <c r="A705" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B705" s="9" t="inlineStr">
@@ -34934,7 +34934,7 @@
     <row r="706">
       <c r="A706" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B706" s="9" t="inlineStr">
@@ -34954,7 +34954,7 @@
       </c>
       <c r="E706" s="9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F706" s="9" t="inlineStr">
@@ -34964,7 +34964,7 @@
       </c>
       <c r="G706" s="9" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H706" s="9" t="inlineStr">
@@ -34976,7 +34976,7 @@
     <row r="707">
       <c r="A707" s="9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B707" s="9" t="inlineStr">
@@ -35018,7 +35018,7 @@
     <row r="708">
       <c r="A708" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B708" s="9" t="inlineStr">
@@ -35060,7 +35060,7 @@
     <row r="709">
       <c r="A709" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B709" s="9" t="inlineStr">
@@ -35102,7 +35102,7 @@
     <row r="710">
       <c r="A710" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B710" s="9" t="inlineStr">
@@ -35144,7 +35144,7 @@
     <row r="711">
       <c r="A711" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B711" s="9" t="inlineStr">
@@ -35186,7 +35186,7 @@
     <row r="712">
       <c r="A712" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B712" s="9" t="inlineStr">
@@ -35228,7 +35228,7 @@
     <row r="713">
       <c r="A713" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B713" s="9" t="inlineStr">
@@ -35270,7 +35270,7 @@
     <row r="714">
       <c r="A714" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B714" s="9" t="inlineStr">
@@ -35312,7 +35312,7 @@
     <row r="715">
       <c r="A715" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B715" s="9" t="inlineStr">
@@ -35354,7 +35354,7 @@
     <row r="716">
       <c r="A716" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B716" s="9" t="inlineStr">
@@ -35374,17 +35374,17 @@
       </c>
       <c r="E716" s="9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F716" s="9" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G716" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="H716" s="9" t="inlineStr">
@@ -35396,7 +35396,7 @@
     <row r="717">
       <c r="A717" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B717" s="9" t="inlineStr">
@@ -35438,7 +35438,7 @@
     <row r="718">
       <c r="A718" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B718" s="9" t="inlineStr">
@@ -35480,7 +35480,7 @@
     <row r="719">
       <c r="A719" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B719" s="9" t="inlineStr">
@@ -35522,7 +35522,7 @@
     <row r="720">
       <c r="A720" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B720" s="9" t="inlineStr">
@@ -35564,7 +35564,7 @@
     <row r="721">
       <c r="A721" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B721" s="9" t="inlineStr">
@@ -35606,7 +35606,7 @@
     <row r="722">
       <c r="A722" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B722" s="9" t="inlineStr">
@@ -35648,7 +35648,7 @@
     <row r="723">
       <c r="A723" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B723" s="9" t="inlineStr">
@@ -35690,7 +35690,7 @@
     <row r="724">
       <c r="A724" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B724" s="9" t="inlineStr">
@@ -35732,7 +35732,7 @@
     <row r="725">
       <c r="A725" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B725" s="9" t="inlineStr">
@@ -35774,7 +35774,7 @@
     <row r="726">
       <c r="A726" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B726" s="9" t="inlineStr">
@@ -35816,7 +35816,7 @@
     <row r="727">
       <c r="A727" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B727" s="9" t="inlineStr">
@@ -35858,7 +35858,7 @@
     <row r="728">
       <c r="A728" s="9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B728" s="9" t="inlineStr">
@@ -35900,7 +35900,7 @@
     <row r="729">
       <c r="A729" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B729" s="9" t="inlineStr">
@@ -35942,7 +35942,7 @@
     <row r="730">
       <c r="A730" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B730" s="9" t="inlineStr">
@@ -35984,7 +35984,7 @@
     <row r="731">
       <c r="A731" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B731" s="9" t="inlineStr">
@@ -36026,7 +36026,7 @@
     <row r="732">
       <c r="A732" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B732" s="9" t="inlineStr">
@@ -36046,7 +36046,7 @@
       </c>
       <c r="E732" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F732" s="9" t="inlineStr">
@@ -36056,7 +36056,7 @@
       </c>
       <c r="G732" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="H732" s="9" t="inlineStr">
@@ -36068,7 +36068,7 @@
     <row r="733">
       <c r="A733" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B733" s="9" t="inlineStr">
@@ -36110,7 +36110,7 @@
     <row r="734">
       <c r="A734" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B734" s="9" t="inlineStr">
@@ -36152,7 +36152,7 @@
     <row r="735">
       <c r="A735" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B735" s="9" t="inlineStr">
@@ -36194,7 +36194,7 @@
     <row r="736">
       <c r="A736" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B736" s="9" t="inlineStr">
@@ -36236,7 +36236,7 @@
     <row r="737">
       <c r="A737" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B737" s="9" t="inlineStr">
@@ -36278,7 +36278,7 @@
     <row r="738">
       <c r="A738" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B738" s="9" t="inlineStr">
@@ -36320,7 +36320,7 @@
     <row r="739">
       <c r="A739" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B739" s="9" t="inlineStr">
@@ -36362,7 +36362,7 @@
     <row r="740">
       <c r="A740" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B740" s="9" t="inlineStr">
@@ -36404,7 +36404,7 @@
     <row r="741">
       <c r="A741" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B741" s="9" t="inlineStr">
@@ -36446,7 +36446,7 @@
     <row r="742">
       <c r="A742" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B742" s="9" t="inlineStr">
@@ -36488,7 +36488,7 @@
     <row r="743">
       <c r="A743" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B743" s="9" t="inlineStr">
@@ -36530,7 +36530,7 @@
     <row r="744">
       <c r="A744" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B744" s="9" t="inlineStr">
@@ -36572,7 +36572,7 @@
     <row r="745">
       <c r="A745" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B745" s="9" t="inlineStr">
@@ -36614,7 +36614,7 @@
     <row r="746">
       <c r="A746" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B746" s="9" t="inlineStr">
@@ -36656,7 +36656,7 @@
     <row r="747">
       <c r="A747" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B747" s="9" t="inlineStr">
@@ -36698,7 +36698,7 @@
     <row r="748">
       <c r="A748" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B748" s="9" t="inlineStr">
@@ -36728,7 +36728,7 @@
       </c>
       <c r="G748" s="9" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>6.75</t>
         </is>
       </c>
       <c r="H748" s="9" t="inlineStr">
@@ -36740,7 +36740,7 @@
     <row r="749">
       <c r="A749" s="9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B749" s="9" t="inlineStr">
@@ -36770,7 +36770,7 @@
       </c>
       <c r="G749" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H749" s="9" t="inlineStr">
@@ -36782,7 +36782,7 @@
     <row r="750">
       <c r="A750" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B750" s="9" t="inlineStr">
@@ -36824,7 +36824,7 @@
     <row r="751">
       <c r="A751" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B751" s="9" t="inlineStr">
@@ -36866,7 +36866,7 @@
     <row r="752">
       <c r="A752" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B752" s="9" t="inlineStr">
@@ -36908,7 +36908,7 @@
     <row r="753">
       <c r="A753" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B753" s="9" t="inlineStr">
@@ -36950,7 +36950,7 @@
     <row r="754">
       <c r="A754" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B754" s="9" t="inlineStr">
@@ -36992,7 +36992,7 @@
     <row r="755">
       <c r="A755" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B755" s="9" t="inlineStr">
@@ -37034,7 +37034,7 @@
     <row r="756">
       <c r="A756" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B756" s="9" t="inlineStr">
@@ -37076,7 +37076,7 @@
     <row r="757">
       <c r="A757" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B757" s="9" t="inlineStr">
@@ -37118,7 +37118,7 @@
     <row r="758">
       <c r="A758" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B758" s="9" t="inlineStr">
@@ -37160,7 +37160,7 @@
     <row r="759">
       <c r="A759" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B759" s="9" t="inlineStr">
@@ -37202,7 +37202,7 @@
     <row r="760">
       <c r="A760" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B760" s="9" t="inlineStr">
@@ -37244,7 +37244,7 @@
     <row r="761">
       <c r="A761" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B761" s="9" t="inlineStr">
@@ -37286,7 +37286,7 @@
     <row r="762">
       <c r="A762" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B762" s="9" t="inlineStr">
@@ -37328,7 +37328,7 @@
     <row r="763">
       <c r="A763" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B763" s="9" t="inlineStr">
@@ -37370,7 +37370,7 @@
     <row r="764">
       <c r="A764" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B764" s="9" t="inlineStr">
@@ -37412,7 +37412,7 @@
     <row r="765">
       <c r="A765" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B765" s="9" t="inlineStr">
@@ -37454,7 +37454,7 @@
     <row r="766">
       <c r="A766" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B766" s="9" t="inlineStr">
@@ -37496,7 +37496,7 @@
     <row r="767">
       <c r="A767" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B767" s="9" t="inlineStr">
@@ -37538,7 +37538,7 @@
     <row r="768">
       <c r="A768" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B768" s="9" t="inlineStr">
@@ -37580,7 +37580,7 @@
     <row r="769">
       <c r="A769" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B769" s="9" t="inlineStr">
@@ -37622,7 +37622,7 @@
     <row r="770">
       <c r="A770" s="9" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B770" s="9" t="inlineStr">
@@ -37664,7 +37664,7 @@
     <row r="771">
       <c r="A771" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B771" s="9" t="inlineStr">
@@ -37706,7 +37706,7 @@
     <row r="772">
       <c r="A772" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B772" s="9" t="inlineStr">
@@ -37748,7 +37748,7 @@
     <row r="773">
       <c r="A773" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B773" s="9" t="inlineStr">
@@ -37790,7 +37790,7 @@
     <row r="774">
       <c r="A774" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B774" s="9" t="inlineStr">
@@ -37832,7 +37832,7 @@
     <row r="775">
       <c r="A775" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B775" s="9" t="inlineStr">
@@ -37874,7 +37874,7 @@
     <row r="776">
       <c r="A776" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B776" s="9" t="inlineStr">
@@ -37916,7 +37916,7 @@
     <row r="777">
       <c r="A777" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B777" s="9" t="inlineStr">
@@ -37958,7 +37958,7 @@
     <row r="778">
       <c r="A778" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B778" s="9" t="inlineStr">
@@ -38000,7 +38000,7 @@
     <row r="779">
       <c r="A779" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B779" s="9" t="inlineStr">
@@ -38042,7 +38042,7 @@
     <row r="780">
       <c r="A780" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B780" s="9" t="inlineStr">
@@ -38084,7 +38084,7 @@
     <row r="781">
       <c r="A781" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B781" s="9" t="inlineStr">
@@ -38126,7 +38126,7 @@
     <row r="782">
       <c r="A782" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B782" s="9" t="inlineStr">
@@ -38168,7 +38168,7 @@
     <row r="783">
       <c r="A783" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B783" s="9" t="inlineStr">
@@ -38210,7 +38210,7 @@
     <row r="784">
       <c r="A784" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B784" s="9" t="inlineStr">
@@ -38252,7 +38252,7 @@
     <row r="785">
       <c r="A785" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B785" s="9" t="inlineStr">
@@ -38294,7 +38294,7 @@
     <row r="786">
       <c r="A786" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B786" s="9" t="inlineStr">
@@ -38336,7 +38336,7 @@
     <row r="787">
       <c r="A787" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B787" s="9" t="inlineStr">
@@ -38378,7 +38378,7 @@
     <row r="788">
       <c r="A788" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B788" s="9" t="inlineStr">
@@ -38420,7 +38420,7 @@
     <row r="789">
       <c r="A789" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B789" s="9" t="inlineStr">
@@ -38462,7 +38462,7 @@
     <row r="790">
       <c r="A790" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B790" s="9" t="inlineStr">
@@ -38504,7 +38504,7 @@
     <row r="791">
       <c r="A791" s="9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B791" s="9" t="inlineStr">
@@ -38546,7 +38546,7 @@
     <row r="792">
       <c r="A792" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B792" s="9" t="inlineStr">
@@ -38576,7 +38576,7 @@
       </c>
       <c r="G792" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H792" s="9" t="inlineStr">
@@ -38588,7 +38588,7 @@
     <row r="793">
       <c r="A793" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B793" s="9" t="inlineStr">
@@ -38630,7 +38630,7 @@
     <row r="794">
       <c r="A794" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B794" s="9" t="inlineStr">
@@ -38672,7 +38672,7 @@
     <row r="795">
       <c r="A795" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B795" s="9" t="inlineStr">
@@ -38714,7 +38714,7 @@
     <row r="796">
       <c r="A796" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B796" s="9" t="inlineStr">
@@ -38756,7 +38756,7 @@
     <row r="797">
       <c r="A797" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B797" s="9" t="inlineStr">
@@ -38798,7 +38798,7 @@
     <row r="798">
       <c r="A798" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B798" s="9" t="inlineStr">
@@ -38840,7 +38840,7 @@
     <row r="799">
       <c r="A799" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B799" s="9" t="inlineStr">
@@ -38882,7 +38882,7 @@
     <row r="800">
       <c r="A800" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B800" s="9" t="inlineStr">
@@ -38924,7 +38924,7 @@
     <row r="801">
       <c r="A801" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B801" s="9" t="inlineStr">
@@ -38966,7 +38966,7 @@
     <row r="802">
       <c r="A802" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B802" s="9" t="inlineStr">
@@ -39008,7 +39008,7 @@
     <row r="803">
       <c r="A803" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B803" s="9" t="inlineStr">
@@ -39050,7 +39050,7 @@
     <row r="804">
       <c r="A804" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B804" s="9" t="inlineStr">
@@ -39092,7 +39092,7 @@
     <row r="805">
       <c r="A805" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B805" s="9" t="inlineStr">
@@ -39134,7 +39134,7 @@
     <row r="806">
       <c r="A806" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B806" s="9" t="inlineStr">
@@ -39176,7 +39176,7 @@
     <row r="807">
       <c r="A807" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B807" s="9" t="inlineStr">
@@ -39218,7 +39218,7 @@
     <row r="808">
       <c r="A808" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B808" s="9" t="inlineStr">
@@ -39260,7 +39260,7 @@
     <row r="809">
       <c r="A809" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B809" s="9" t="inlineStr">
@@ -39302,7 +39302,7 @@
     <row r="810">
       <c r="A810" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B810" s="9" t="inlineStr">
@@ -39344,7 +39344,7 @@
     <row r="811">
       <c r="A811" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B811" s="9" t="inlineStr">
@@ -39386,7 +39386,7 @@
     <row r="812">
       <c r="A812" s="9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B812" s="9" t="inlineStr">
@@ -39416,7 +39416,7 @@
       </c>
       <c r="G812" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H812" s="9" t="inlineStr">
@@ -39428,7 +39428,7 @@
     <row r="813">
       <c r="A813" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B813" s="9" t="inlineStr">
@@ -39458,7 +39458,7 @@
       </c>
       <c r="G813" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H813" s="9" t="inlineStr">
@@ -39470,7 +39470,7 @@
     <row r="814">
       <c r="A814" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B814" s="9" t="inlineStr">
@@ -39512,7 +39512,7 @@
     <row r="815">
       <c r="A815" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B815" s="9" t="inlineStr">
@@ -39554,7 +39554,7 @@
     <row r="816">
       <c r="A816" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B816" s="9" t="inlineStr">
@@ -39574,7 +39574,7 @@
       </c>
       <c r="E816" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F816" s="9" t="inlineStr">
@@ -39584,7 +39584,7 @@
       </c>
       <c r="G816" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H816" s="9" t="inlineStr">
@@ -39596,7 +39596,7 @@
     <row r="817">
       <c r="A817" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B817" s="9" t="inlineStr">
@@ -39638,7 +39638,7 @@
     <row r="818">
       <c r="A818" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B818" s="9" t="inlineStr">
@@ -39658,17 +39658,17 @@
       </c>
       <c r="E818" s="9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F818" s="9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Elevated</t>
         </is>
       </c>
       <c r="G818" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H818" s="9" t="inlineStr">
@@ -39680,7 +39680,7 @@
     <row r="819">
       <c r="A819" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B819" s="9" t="inlineStr">
@@ -39722,7 +39722,7 @@
     <row r="820">
       <c r="A820" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B820" s="9" t="inlineStr">
@@ -39764,7 +39764,7 @@
     <row r="821">
       <c r="A821" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B821" s="9" t="inlineStr">
@@ -39784,7 +39784,7 @@
       </c>
       <c r="E821" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F821" s="9" t="inlineStr">
@@ -39794,7 +39794,7 @@
       </c>
       <c r="G821" s="9" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="H821" s="9" t="inlineStr">
@@ -39806,7 +39806,7 @@
     <row r="822">
       <c r="A822" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B822" s="9" t="inlineStr">
@@ -39848,7 +39848,7 @@
     <row r="823">
       <c r="A823" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B823" s="9" t="inlineStr">
@@ -39890,7 +39890,7 @@
     <row r="824">
       <c r="A824" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B824" s="9" t="inlineStr">
@@ -39932,7 +39932,7 @@
     <row r="825">
       <c r="A825" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B825" s="9" t="inlineStr">
@@ -39974,7 +39974,7 @@
     <row r="826">
       <c r="A826" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B826" s="9" t="inlineStr">
@@ -40016,7 +40016,7 @@
     <row r="827">
       <c r="A827" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B827" s="9" t="inlineStr">
@@ -40036,17 +40036,17 @@
       </c>
       <c r="E827" s="9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F827" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G827" s="9" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="H827" s="9" t="inlineStr">
@@ -40058,7 +40058,7 @@
     <row r="828">
       <c r="A828" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B828" s="9" t="inlineStr">
@@ -40100,7 +40100,7 @@
     <row r="829">
       <c r="A829" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B829" s="9" t="inlineStr">
@@ -40120,17 +40120,17 @@
       </c>
       <c r="E829" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F829" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G829" s="9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H829" s="9" t="inlineStr">
@@ -40142,7 +40142,7 @@
     <row r="830">
       <c r="A830" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B830" s="9" t="inlineStr">
@@ -40184,7 +40184,7 @@
     <row r="831">
       <c r="A831" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B831" s="9" t="inlineStr">
@@ -40226,7 +40226,7 @@
     <row r="832">
       <c r="A832" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B832" s="9" t="inlineStr">
@@ -40256,7 +40256,7 @@
       </c>
       <c r="G832" s="9" t="inlineStr">
         <is>
-          <t>6.75</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="H832" s="9" t="inlineStr">
@@ -40268,7 +40268,7 @@
     <row r="833">
       <c r="A833" s="9" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B833" s="9" t="inlineStr">
@@ -40298,7 +40298,7 @@
       </c>
       <c r="G833" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H833" s="9" t="inlineStr">
@@ -40310,7 +40310,7 @@
     <row r="834">
       <c r="A834" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B834" s="9" t="inlineStr">
@@ -40340,7 +40340,7 @@
       </c>
       <c r="G834" s="9" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="H834" s="9" t="inlineStr">
@@ -40352,7 +40352,7 @@
     <row r="835">
       <c r="A835" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B835" s="9" t="inlineStr">
@@ -40394,7 +40394,7 @@
     <row r="836">
       <c r="A836" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B836" s="9" t="inlineStr">
@@ -40436,7 +40436,7 @@
     <row r="837">
       <c r="A837" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B837" s="9" t="inlineStr">
@@ -40478,7 +40478,7 @@
     <row r="838">
       <c r="A838" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B838" s="9" t="inlineStr">
@@ -40520,7 +40520,7 @@
     <row r="839">
       <c r="A839" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B839" s="9" t="inlineStr">
@@ -40562,7 +40562,7 @@
     <row r="840">
       <c r="A840" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B840" s="9" t="inlineStr">
@@ -40604,7 +40604,7 @@
     <row r="841">
       <c r="A841" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B841" s="9" t="inlineStr">
@@ -40646,7 +40646,7 @@
     <row r="842">
       <c r="A842" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B842" s="9" t="inlineStr">
@@ -40688,7 +40688,7 @@
     <row r="843">
       <c r="A843" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B843" s="9" t="inlineStr">
@@ -40730,7 +40730,7 @@
     <row r="844">
       <c r="A844" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B844" s="9" t="inlineStr">
@@ -40772,7 +40772,7 @@
     <row r="845">
       <c r="A845" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B845" s="9" t="inlineStr">
@@ -40814,7 +40814,7 @@
     <row r="846">
       <c r="A846" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B846" s="9" t="inlineStr">
@@ -40856,7 +40856,7 @@
     <row r="847">
       <c r="A847" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B847" s="9" t="inlineStr">
@@ -40898,7 +40898,7 @@
     <row r="848">
       <c r="A848" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B848" s="9" t="inlineStr">
@@ -40940,7 +40940,7 @@
     <row r="849">
       <c r="A849" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B849" s="9" t="inlineStr">
@@ -40982,7 +40982,7 @@
     <row r="850">
       <c r="A850" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B850" s="9" t="inlineStr">
@@ -41024,7 +41024,7 @@
     <row r="851">
       <c r="A851" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B851" s="9" t="inlineStr">
@@ -41066,7 +41066,7 @@
     <row r="852">
       <c r="A852" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B852" s="9" t="inlineStr">
@@ -41108,7 +41108,7 @@
     <row r="853">
       <c r="A853" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B853" s="9" t="inlineStr">
@@ -41150,7 +41150,7 @@
     <row r="854">
       <c r="A854" s="9" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B854" s="9" t="inlineStr">
@@ -41180,7 +41180,7 @@
       </c>
       <c r="G854" s="9" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="H854" s="9" t="inlineStr">
@@ -41192,7 +41192,7 @@
     <row r="855">
       <c r="A855" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B855" s="9" t="inlineStr">
@@ -41234,7 +41234,7 @@
     <row r="856">
       <c r="A856" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B856" s="9" t="inlineStr">
@@ -41276,7 +41276,7 @@
     <row r="857">
       <c r="A857" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B857" s="9" t="inlineStr">
@@ -41318,7 +41318,7 @@
     <row r="858">
       <c r="A858" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B858" s="9" t="inlineStr">
@@ -41360,7 +41360,7 @@
     <row r="859">
       <c r="A859" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B859" s="9" t="inlineStr">
@@ -41402,7 +41402,7 @@
     <row r="860">
       <c r="A860" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B860" s="9" t="inlineStr">
@@ -41444,7 +41444,7 @@
     <row r="861">
       <c r="A861" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B861" s="9" t="inlineStr">
@@ -41486,7 +41486,7 @@
     <row r="862">
       <c r="A862" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B862" s="9" t="inlineStr">
@@ -41528,7 +41528,7 @@
     <row r="863">
       <c r="A863" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B863" s="9" t="inlineStr">
@@ -41570,7 +41570,7 @@
     <row r="864">
       <c r="A864" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B864" s="9" t="inlineStr">
@@ -41612,7 +41612,7 @@
     <row r="865">
       <c r="A865" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B865" s="9" t="inlineStr">
@@ -41654,7 +41654,7 @@
     <row r="866">
       <c r="A866" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B866" s="9" t="inlineStr">
@@ -41696,7 +41696,7 @@
     <row r="867">
       <c r="A867" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B867" s="9" t="inlineStr">
@@ -41738,7 +41738,7 @@
     <row r="868">
       <c r="A868" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B868" s="9" t="inlineStr">
@@ -41780,7 +41780,7 @@
     <row r="869">
       <c r="A869" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B869" s="9" t="inlineStr">
@@ -41822,7 +41822,7 @@
     <row r="870">
       <c r="A870" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B870" s="9" t="inlineStr">
@@ -41864,7 +41864,7 @@
     <row r="871">
       <c r="A871" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B871" s="9" t="inlineStr">
@@ -41906,7 +41906,7 @@
     <row r="872">
       <c r="A872" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B872" s="9" t="inlineStr">
@@ -41948,7 +41948,7 @@
     <row r="873">
       <c r="A873" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B873" s="9" t="inlineStr">
@@ -41990,7 +41990,7 @@
     <row r="874">
       <c r="A874" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B874" s="9" t="inlineStr">
@@ -42032,7 +42032,7 @@
     <row r="875">
       <c r="A875" s="9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B875" s="9" t="inlineStr">
@@ -42074,7 +42074,7 @@
     <row r="876">
       <c r="A876" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B876" s="9" t="inlineStr">
@@ -42116,7 +42116,7 @@
     <row r="877">
       <c r="A877" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B877" s="9" t="inlineStr">
@@ -42158,7 +42158,7 @@
     <row r="878">
       <c r="A878" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B878" s="9" t="inlineStr">
@@ -42200,7 +42200,7 @@
     <row r="879">
       <c r="A879" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B879" s="9" t="inlineStr">
@@ -42242,7 +42242,7 @@
     <row r="880">
       <c r="A880" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B880" s="9" t="inlineStr">
@@ -42284,7 +42284,7 @@
     <row r="881">
       <c r="A881" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B881" s="9" t="inlineStr">
@@ -42326,7 +42326,7 @@
     <row r="882">
       <c r="A882" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B882" s="9" t="inlineStr">
@@ -42368,7 +42368,7 @@
     <row r="883">
       <c r="A883" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B883" s="9" t="inlineStr">
@@ -42410,7 +42410,7 @@
     <row r="884">
       <c r="A884" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B884" s="9" t="inlineStr">
@@ -42452,7 +42452,7 @@
     <row r="885">
       <c r="A885" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B885" s="9" t="inlineStr">
@@ -42494,7 +42494,7 @@
     <row r="886">
       <c r="A886" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B886" s="9" t="inlineStr">
@@ -42536,7 +42536,7 @@
     <row r="887">
       <c r="A887" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B887" s="9" t="inlineStr">
@@ -42578,7 +42578,7 @@
     <row r="888">
       <c r="A888" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B888" s="9" t="inlineStr">
@@ -42620,7 +42620,7 @@
     <row r="889">
       <c r="A889" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B889" s="9" t="inlineStr">
@@ -42662,7 +42662,7 @@
     <row r="890">
       <c r="A890" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B890" s="9" t="inlineStr">
@@ -42704,7 +42704,7 @@
     <row r="891">
       <c r="A891" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B891" s="9" t="inlineStr">
@@ -42746,7 +42746,7 @@
     <row r="892">
       <c r="A892" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B892" s="9" t="inlineStr">
@@ -42788,7 +42788,7 @@
     <row r="893">
       <c r="A893" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B893" s="9" t="inlineStr">
@@ -42830,7 +42830,7 @@
     <row r="894">
       <c r="A894" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B894" s="9" t="inlineStr">
@@ -42872,7 +42872,7 @@
     <row r="895">
       <c r="A895" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B895" s="9" t="inlineStr">
@@ -42914,7 +42914,7 @@
     <row r="896">
       <c r="A896" s="9" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B896" s="9" t="inlineStr">
@@ -42956,7 +42956,7 @@
     <row r="897">
       <c r="A897" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B897" s="9" t="inlineStr">
@@ -42998,7 +42998,7 @@
     <row r="898">
       <c r="A898" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B898" s="9" t="inlineStr">
@@ -43040,7 +43040,7 @@
     <row r="899">
       <c r="A899" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B899" s="9" t="inlineStr">
@@ -43082,7 +43082,7 @@
     <row r="900">
       <c r="A900" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B900" s="9" t="inlineStr">
@@ -43124,7 +43124,7 @@
     <row r="901">
       <c r="A901" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B901" s="9" t="inlineStr">
@@ -43166,7 +43166,7 @@
     <row r="902">
       <c r="A902" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B902" s="9" t="inlineStr">
@@ -43208,7 +43208,7 @@
     <row r="903">
       <c r="A903" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B903" s="9" t="inlineStr">
@@ -43250,7 +43250,7 @@
     <row r="904">
       <c r="A904" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B904" s="9" t="inlineStr">
@@ -43292,7 +43292,7 @@
     <row r="905">
       <c r="A905" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B905" s="9" t="inlineStr">
@@ -43334,7 +43334,7 @@
     <row r="906">
       <c r="A906" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B906" s="9" t="inlineStr">
@@ -43376,7 +43376,7 @@
     <row r="907">
       <c r="A907" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B907" s="9" t="inlineStr">
@@ -43418,7 +43418,7 @@
     <row r="908">
       <c r="A908" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B908" s="9" t="inlineStr">
@@ -43460,7 +43460,7 @@
     <row r="909">
       <c r="A909" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B909" s="9" t="inlineStr">
@@ -43502,7 +43502,7 @@
     <row r="910">
       <c r="A910" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B910" s="9" t="inlineStr">
@@ -43544,7 +43544,7 @@
     <row r="911">
       <c r="A911" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B911" s="9" t="inlineStr">
@@ -43586,7 +43586,7 @@
     <row r="912">
       <c r="A912" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B912" s="9" t="inlineStr">
@@ -43628,7 +43628,7 @@
     <row r="913">
       <c r="A913" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B913" s="9" t="inlineStr">
@@ -43670,7 +43670,7 @@
     <row r="914">
       <c r="A914" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B914" s="9" t="inlineStr">
@@ -43712,7 +43712,7 @@
     <row r="915">
       <c r="A915" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B915" s="9" t="inlineStr">
@@ -43754,7 +43754,7 @@
     <row r="916">
       <c r="A916" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B916" s="9" t="inlineStr">
@@ -43796,7 +43796,7 @@
     <row r="917">
       <c r="A917" s="9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B917" s="9" t="inlineStr">
@@ -43838,7 +43838,7 @@
     <row r="918">
       <c r="A918" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B918" s="9" t="inlineStr">
@@ -43880,7 +43880,7 @@
     <row r="919">
       <c r="A919" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B919" s="9" t="inlineStr">
@@ -43922,7 +43922,7 @@
     <row r="920">
       <c r="A920" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B920" s="9" t="inlineStr">
@@ -43964,7 +43964,7 @@
     <row r="921">
       <c r="A921" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B921" s="9" t="inlineStr">
@@ -44006,7 +44006,7 @@
     <row r="922">
       <c r="A922" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B922" s="9" t="inlineStr">
@@ -44048,7 +44048,7 @@
     <row r="923">
       <c r="A923" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B923" s="9" t="inlineStr">
@@ -44090,7 +44090,7 @@
     <row r="924">
       <c r="A924" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B924" s="9" t="inlineStr">
@@ -44132,7 +44132,7 @@
     <row r="925">
       <c r="A925" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B925" s="9" t="inlineStr">
@@ -44174,7 +44174,7 @@
     <row r="926">
       <c r="A926" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B926" s="9" t="inlineStr">
@@ -44216,7 +44216,7 @@
     <row r="927">
       <c r="A927" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B927" s="9" t="inlineStr">
@@ -44258,7 +44258,7 @@
     <row r="928">
       <c r="A928" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B928" s="9" t="inlineStr">
@@ -44300,7 +44300,7 @@
     <row r="929">
       <c r="A929" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B929" s="9" t="inlineStr">
@@ -44342,7 +44342,7 @@
     <row r="930">
       <c r="A930" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B930" s="9" t="inlineStr">
@@ -44384,7 +44384,7 @@
     <row r="931">
       <c r="A931" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B931" s="9" t="inlineStr">
@@ -44426,7 +44426,7 @@
     <row r="932">
       <c r="A932" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B932" s="9" t="inlineStr">
@@ -44468,7 +44468,7 @@
     <row r="933">
       <c r="A933" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B933" s="9" t="inlineStr">
@@ -44510,7 +44510,7 @@
     <row r="934">
       <c r="A934" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B934" s="9" t="inlineStr">
@@ -44552,7 +44552,7 @@
     <row r="935">
       <c r="A935" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B935" s="9" t="inlineStr">
@@ -44594,7 +44594,7 @@
     <row r="936">
       <c r="A936" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B936" s="9" t="inlineStr">
@@ -44636,7 +44636,7 @@
     <row r="937">
       <c r="A937" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B937" s="9" t="inlineStr">
@@ -44678,7 +44678,7 @@
     <row r="938">
       <c r="A938" s="9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B938" s="9" t="inlineStr">
@@ -44720,7 +44720,7 @@
     <row r="939">
       <c r="A939" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B939" s="9" t="inlineStr">
@@ -44762,7 +44762,7 @@
     <row r="940">
       <c r="A940" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B940" s="9" t="inlineStr">
@@ -44804,7 +44804,7 @@
     <row r="941">
       <c r="A941" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B941" s="9" t="inlineStr">
@@ -44846,7 +44846,7 @@
     <row r="942">
       <c r="A942" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B942" s="9" t="inlineStr">
@@ -44888,7 +44888,7 @@
     <row r="943">
       <c r="A943" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B943" s="9" t="inlineStr">
@@ -44930,7 +44930,7 @@
     <row r="944">
       <c r="A944" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B944" s="9" t="inlineStr">
@@ -44972,7 +44972,7 @@
     <row r="945">
       <c r="A945" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B945" s="9" t="inlineStr">
@@ -45014,7 +45014,7 @@
     <row r="946">
       <c r="A946" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B946" s="9" t="inlineStr">
@@ -45056,7 +45056,7 @@
     <row r="947">
       <c r="A947" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B947" s="9" t="inlineStr">
@@ -45098,7 +45098,7 @@
     <row r="948">
       <c r="A948" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B948" s="9" t="inlineStr">
@@ -45140,7 +45140,7 @@
     <row r="949">
       <c r="A949" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B949" s="9" t="inlineStr">
@@ -45182,7 +45182,7 @@
     <row r="950">
       <c r="A950" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B950" s="9" t="inlineStr">
@@ -45224,7 +45224,7 @@
     <row r="951">
       <c r="A951" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B951" s="9" t="inlineStr">
@@ -45266,7 +45266,7 @@
     <row r="952">
       <c r="A952" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B952" s="9" t="inlineStr">
@@ -45308,7 +45308,7 @@
     <row r="953">
       <c r="A953" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B953" s="9" t="inlineStr">
@@ -45350,7 +45350,7 @@
     <row r="954">
       <c r="A954" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B954" s="9" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="955">
       <c r="A955" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B955" s="9" t="inlineStr">
@@ -45434,7 +45434,7 @@
     <row r="956">
       <c r="A956" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B956" s="9" t="inlineStr">
@@ -45476,7 +45476,7 @@
     <row r="957">
       <c r="A957" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B957" s="9" t="inlineStr">
@@ -45518,7 +45518,7 @@
     <row r="958">
       <c r="A958" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B958" s="9" t="inlineStr">
@@ -45560,7 +45560,7 @@
     <row r="959">
       <c r="A959" s="9" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B959" s="9" t="inlineStr">
@@ -45602,7 +45602,7 @@
     <row r="960">
       <c r="A960" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B960" s="9" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="G960" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H960" s="9" t="inlineStr">
@@ -45644,7 +45644,7 @@
     <row r="961">
       <c r="A961" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B961" s="9" t="inlineStr">
@@ -45686,7 +45686,7 @@
     <row r="962">
       <c r="A962" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B962" s="9" t="inlineStr">
@@ -45728,7 +45728,7 @@
     <row r="963">
       <c r="A963" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B963" s="9" t="inlineStr">
@@ -45770,7 +45770,7 @@
     <row r="964">
       <c r="A964" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B964" s="9" t="inlineStr">
@@ -45812,7 +45812,7 @@
     <row r="965">
       <c r="A965" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B965" s="9" t="inlineStr">
@@ -45854,7 +45854,7 @@
     <row r="966">
       <c r="A966" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B966" s="9" t="inlineStr">
@@ -45896,7 +45896,7 @@
     <row r="967">
       <c r="A967" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B967" s="9" t="inlineStr">
@@ -45938,7 +45938,7 @@
     <row r="968">
       <c r="A968" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B968" s="9" t="inlineStr">
@@ -45980,7 +45980,7 @@
     <row r="969">
       <c r="A969" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B969" s="9" t="inlineStr">
@@ -46022,7 +46022,7 @@
     <row r="970">
       <c r="A970" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B970" s="9" t="inlineStr">
@@ -46064,7 +46064,7 @@
     <row r="971">
       <c r="A971" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B971" s="9" t="inlineStr">
@@ -46106,7 +46106,7 @@
     <row r="972">
       <c r="A972" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B972" s="9" t="inlineStr">
@@ -46148,7 +46148,7 @@
     <row r="973">
       <c r="A973" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B973" s="9" t="inlineStr">
@@ -46190,7 +46190,7 @@
     <row r="974">
       <c r="A974" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B974" s="9" t="inlineStr">
@@ -46232,7 +46232,7 @@
     <row r="975">
       <c r="A975" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B975" s="9" t="inlineStr">
@@ -46274,7 +46274,7 @@
     <row r="976">
       <c r="A976" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B976" s="9" t="inlineStr">
@@ -46316,7 +46316,7 @@
     <row r="977">
       <c r="A977" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B977" s="9" t="inlineStr">
@@ -46358,7 +46358,7 @@
     <row r="978">
       <c r="A978" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B978" s="9" t="inlineStr">
@@ -46400,7 +46400,7 @@
     <row r="979">
       <c r="A979" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B979" s="9" t="inlineStr">
@@ -46442,7 +46442,7 @@
     <row r="980">
       <c r="A980" s="9" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B980" s="9" t="inlineStr">
@@ -46472,7 +46472,7 @@
       </c>
       <c r="G980" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H980" s="9" t="inlineStr">
@@ -46484,7 +46484,7 @@
     <row r="981">
       <c r="A981" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B981" s="9" t="inlineStr">
@@ -46526,7 +46526,7 @@
     <row r="982">
       <c r="A982" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B982" s="9" t="inlineStr">
@@ -46568,7 +46568,7 @@
     <row r="983">
       <c r="A983" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B983" s="9" t="inlineStr">
@@ -46610,7 +46610,7 @@
     <row r="984">
       <c r="A984" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B984" s="9" t="inlineStr">
@@ -46652,7 +46652,7 @@
     <row r="985">
       <c r="A985" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B985" s="9" t="inlineStr">
@@ -46694,7 +46694,7 @@
     <row r="986">
       <c r="A986" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B986" s="9" t="inlineStr">
@@ -46736,7 +46736,7 @@
     <row r="987">
       <c r="A987" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B987" s="9" t="inlineStr">
@@ -46778,7 +46778,7 @@
     <row r="988">
       <c r="A988" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B988" s="9" t="inlineStr">
@@ -46820,7 +46820,7 @@
     <row r="989">
       <c r="A989" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B989" s="9" t="inlineStr">
@@ -46862,7 +46862,7 @@
     <row r="990">
       <c r="A990" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B990" s="9" t="inlineStr">
@@ -46904,7 +46904,7 @@
     <row r="991">
       <c r="A991" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B991" s="9" t="inlineStr">
@@ -46946,7 +46946,7 @@
     <row r="992">
       <c r="A992" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B992" s="9" t="inlineStr">
@@ -46988,7 +46988,7 @@
     <row r="993">
       <c r="A993" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B993" s="9" t="inlineStr">
@@ -47030,7 +47030,7 @@
     <row r="994">
       <c r="A994" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B994" s="9" t="inlineStr">
@@ -47072,7 +47072,7 @@
     <row r="995">
       <c r="A995" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B995" s="9" t="inlineStr">
@@ -47114,7 +47114,7 @@
     <row r="996">
       <c r="A996" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B996" s="9" t="inlineStr">
@@ -47156,7 +47156,7 @@
     <row r="997">
       <c r="A997" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B997" s="9" t="inlineStr">
@@ -47198,7 +47198,7 @@
     <row r="998">
       <c r="A998" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B998" s="9" t="inlineStr">
@@ -47240,7 +47240,7 @@
     <row r="999">
       <c r="A999" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B999" s="9" t="inlineStr">
@@ -47282,7 +47282,7 @@
     <row r="1000">
       <c r="A1000" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B1000" s="9" t="inlineStr">
@@ -47324,7 +47324,7 @@
     <row r="1001">
       <c r="A1001" s="9" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="B1001" s="9" t="inlineStr">
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47455,7 +47455,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>--- Daily narrative (2026-10-08) ---</t>
+          <t>--- Daily narrative (2026-10-09) ---</t>
         </is>
       </c>
     </row>
@@ -47469,7 +47469,7 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands High, driven by opacity in private credit, Japan's carry-trade vulnerabilities, and critical infrastructure chokepoints.</t>
+          <t>Macro risk stands at High, driven by structural leverage and supply-chain vulnerabilities across finance, energy, and geopolitics.</t>
         </is>
       </c>
     </row>
@@ -47479,37 +47479,49 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**STORIES (no intraday changes recorded)**</t>
+          <t>**KEY STORIES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>• **Private credit's opaque expansion** (High): Rapid growth in unregulated lending channels with limited transparency on counterparty health and redemption mechanics creates systemic contagion risk.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>• **Private credit's opaque expansion** (High): Unregulated growth in shadow lending creates systemic contagion risk if liquidity dries or counterparties fail.</t>
+          <t>• **AI power &amp; the grid bottleneck** (High): Data center demand outpacing grid capacity and power infrastructure investment; operational or procurement disruptions could cascade.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>• **Japan fiscal / JGB / carry trade** (High): Fiscal stress and unwinding carry positions remain acute; volatility spillover to global rates and FX markets.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>• **Japan fiscal / JGB / carry trade** (High): Structural imbalances and yen sensitivity threaten unwinding cascades across global FX and equity markets.</t>
+          <t>• **Sea lanes &amp; undersea cables** (High): Geopolitical and physical threats to critical infrastructure for trade and data; no swift redundancy.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr"/>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>• **Treasury basis trade (hidden leverage)** (Elevated): Repo-financed arbitrage concentrates duration risk; forced deleveraging would amplify volatility.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>• **AI power &amp; the grid bottleneck** (High): Surging AI compute demand strains electricity supply, risking blackouts and capex shortfalls in data-center buildout.</t>
+          <t>• **Developing-world debt crisis, CRE maturity wall, China deflation spillover, critical minerals weaponization, AI circular financing, lithography chokepoint, food fragility, eurozone friction** (Elevated): Each poses medium-term refinancing, contagion, or supply shock risk.</t>
         </is>
       </c>
     </row>
@@ -47519,37 +47531,7 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>• **Sea lanes &amp; undersea cables** (High): Geopolitical friction and infrastructure vulnerability threaten supply chains and digital connectivity.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>• **Treasury basis trade** (Elevated): Hidden leverage in basis arbitrage could amplify volatility if funding conditions tighten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="12" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>• **Developing-world debt crisis, China spillover, critical minerals, AI financing, CRE maturity wall, eurozone fragility, consumer debt, food fragility, lithography chokepoint** (Elevated): Each poses material tail risk to credit, commodity, or supply-chain stability.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>**WATCH:** Private credit opacity remains the highest-risk story—systemic exposure is unmeasured and contagion speed is unknowable.</t>
+          <t>**WATCH CLOSEST:** Private credit's opaque expansion—largest absolute risk level (8) with lowest institutional visibility.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-10-13  -  generated 2026-10-13 13:50 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-10-13  -  generated 2026-10-13 14:29 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>100.6772</v>
+        <v>100.7189</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.39</v>
+        <v>158.375</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6806</v>
+        <v>6.6808</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4209.6001</v>
+        <v>4189.5</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.7575</v>
+        <v>6.7375</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>92.78</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.26</v>
+        <v>15.24</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>100.6772</v>
+        <v>100.7189</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -47462,37 +47462,41 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro Risk Brief | 13 Oct 2026</t>
+          <t>**Headline**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Macro risk stands at High overall, with five stories at High or above: Japan fiscal/JGB/carry trade, Private credit's opaque expansion, Critical minerals as a weapon, AI power &amp; the grid bottleneck, and Sea lanes &amp; undersea cables.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Overall risk sentiment is High, with no intraday changes to tracked stories.**</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**No stories changed bands since the previous run.**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>No stories shifted bands today. The portfolio remains anchored by four High-rated risks: Private credit's opaque expansion (8/10—the largest single exposure, reflecting unmonitored leverage in non-bank lending); Japan fiscal/JGB/carry trade (7/10—structural imbalance in sovereign debt and FX positioning); Critical minerals as a weapon (7/10—geopolitical supply concentration); and AI power &amp; the grid bottleneck (7/10—infrastructure inadequacy for demand). Nine additional stories remain Elevated, spanning Treasury basis trades, developing-world debt, China deflation spillover, CRE maturity stress, and supply-chain chokepoints.</t>
-        </is>
-      </c>
+      <c r="A18" s="12" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>**Watch list**</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>**Watch: Private credit's opaque expansion—largest systemic risk by score and most resistant to policy visibility.**</t>
+          <t>Private credit's opaque expansion remains the single highest-risk story at level 8.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-10-13  -  generated 2026-10-13 14:29 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-10-13  -  generated 2026-10-13 14:53 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>100.7189</v>
+        <v>100.6915</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.375</v>
+        <v>158.36</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4189.5</v>
+        <v>4191.5</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.7375</v>
+        <v>6.738</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>93.68000000000001</v>
+        <v>93.77</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>100.7189</v>
+        <v>100.6915</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47462,14 +47462,14 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**Headline**</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Macro risk stands at High overall, with five stories at High or above: Japan fiscal/JGB/carry trade, Private credit's opaque expansion, Critical minerals as a weapon, AI power &amp; the grid bottleneck, and Sea lanes &amp; undersea cables.</t>
+          <t>Macro risk stands at High, with 5 stories at High or above and no intraday moves.</t>
         </is>
       </c>
     </row>
@@ -47479,24 +47479,31 @@
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>**No stories changed bands since the previous run.**</t>
+          <t>**STORY CHANGES**</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr"/>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>No stories experienced level changes today.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>**Watch list**</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion remains the single highest-risk story at level 8.</t>
+          <t>**HIGHEST-RISK WATCH**</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion remains the most acute risk at level 8.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-10-13  -  generated 2026-10-13 14:53 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-10-13  -  generated 2026-10-13 16:14 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>100.6915</v>
+        <v>100.6698</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.36</v>
+        <v>158.349</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4191.5</v>
+        <v>4181</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.738</v>
+        <v>6.723</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>93.77</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.24</v>
+        <v>15.44</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>100.6915</v>
+        <v>100.6698</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47462,48 +47462,68 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**HEADLINE**</t>
+          <t># EOD Macro-Risk Brief | 2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>Macro risk stands at High, with 5 stories at High or above and no intraday moves.</t>
-        </is>
-      </c>
+      <c r="A15" s="12" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr"/>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>**Headline:** Overall macro risk stands at High with no intraday moves; five stories remain at High severity.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>**STORY CHANGES**</t>
-        </is>
-      </c>
+      <c r="A17" s="12" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>No stories experienced level changes today.</t>
+          <t>**Changed Stories:**</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr"/>
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>None. No driver shifts occurred today.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>**HIGHEST-RISK WATCH**</t>
-        </is>
-      </c>
+      <c r="A20" s="12" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion remains the most acute risk at level 8.</t>
+          <t>**Stories at High or Above:**</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion, Japan fiscal / JGB / carry trade, Critical minerals as a weapon, AI power &amp; the grid bottleneck, and Sea lanes &amp; undersea cables remain the five elevated focal points.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>**Watch Priority:**</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Private credit's opaque expansion (level 8, High) remains the single highest-risk story to monitor.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-10-13  -  generated 2026-10-13 16:14 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-10-13  -  generated 2026-10-13 18:29 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>100.6698</v>
+        <v>100.9292</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.349</v>
+        <v>158.331</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6808</v>
+        <v>6.6807</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2578,7 +2578,7 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>312.9</v>
+        <v>313.1</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4181</v>
+        <v>4183.2002</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.723</v>
+        <v>6.732</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>93.90000000000001</v>
+        <v>94.36</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.44</v>
+        <v>15.41</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>100.6698</v>
+        <v>100.9292</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -47462,68 +47462,48 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t># EOD Macro-Risk Brief | 2026-10-13</t>
+          <t>**HEADLINE**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr"/>
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Overall macro risk stands at High, with five stories at High or above and no changes in driver readings since yesterday.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>**Headline:** Overall macro risk stands at High with no intraday moves; five stories remain at High severity.</t>
-        </is>
-      </c>
+      <c r="A16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr"/>
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>**UNCHANGED STORIES**</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Changed Stories:**</t>
+          <t>No stories moved today. All 5 n_stories_at_high_or_above remain at High: Japan fiscal / JGB / carry trade, Private credit's opaque expansion, Critical minerals as a weapon, AI power &amp; the grid bottleneck, and Sea lanes &amp; undersea cables. Risk to financial stability and supply-chain resilience persists without new triggering conditions.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>None. No driver shifts occurred today.</t>
-        </is>
-      </c>
+      <c r="A19" s="12" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr"/>
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>**TOP WATCH**</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>**Stories at High or Above:**</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion, Japan fiscal / JGB / carry trade, Critical minerals as a weapon, AI power &amp; the grid bottleneck, and Sea lanes &amp; undersea cables remain the five elevated focal points.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>**Watch Priority:**</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Private credit's opaque expansion (level 8, High) remains the single highest-risk story to monitor.</t>
+          <t>Private credit's opaque expansion (High) poses the sharpest near-term risk given its rapid growth outside regulated banking channels and opacity to systemic stress.</t>
         </is>
       </c>
     </row>

--- a/output/macro_risk_tracker.xlsx
+++ b/output/macro_risk_tracker.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As of 2026-10-14  -  generated 2026-10-14 10:16 UTC  -  levels recalculated from the Indicators tab</t>
+          <t>As of 2026-10-14  -  generated 2026-10-14 15:57 UTC  -  levels recalculated from the Indicators tab</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="D2" s="7" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
         </is>
       </c>
       <c r="D3" s="7" t="n">
-        <v>101.09</v>
+        <v>99.9363</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         </is>
       </c>
       <c r="D5" s="7" t="n">
-        <v>158.456</v>
+        <v>158.795</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
         </is>
       </c>
       <c r="D15" s="7" t="n">
-        <v>6.6811</v>
+        <v>6.6867</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>312.3</v>
+        <v>309.8</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4165.1001</v>
+        <v>4107</v>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="D47" s="7" t="n">
-        <v>6.73</v>
+        <v>6.665</v>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         </is>
       </c>
       <c r="D60" s="7" t="n">
-        <v>95.27</v>
+        <v>94.98999999999999</v>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="D62" s="7" t="n">
-        <v>15.22</v>
+        <v>16.15</v>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
         </is>
       </c>
       <c r="D63" s="7" t="n">
-        <v>101.09</v>
+        <v>99.9363</v>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
@@ -46604,7 +46604,7 @@
       </c>
       <c r="G981" s="9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="H981" s="9" t="inlineStr">
@@ -47434,17 +47434,17 @@
       </c>
       <c r="E1001" s="9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F1001" s="9" t="inlineStr">
         <is>
-          <t>Elevated</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="G1001" s="9" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="H1001" s="9" t="inlineStr">
@@ -47552,7 +47552,7 @@
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>**Macro Risk EOD Brief | 14 October 2026**</t>
+          <t># EOD Macro-Risk Brief | 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -47562,7 +47562,7 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>**Headline:** Overall macro risk is High, with 8 stories at High or above and no intraday moves.</t>
+          <t>**Overall risk remains High, with eight stories at High band or above.**</t>
         </is>
       </c>
     </row>
@@ -47572,14 +47572,14 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>**Key Stories:**</t>
+          <t>**Changed story:**</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>No stories changed band since the previous run.</t>
+          <t>- **Clearinghouses (financial chokepoint)** moved from Moderate to Moderate. Treasury volatility (MOVE index) declined to 99.94 from 101.09, reducing acute stress on central counterparty infrastructure and the risk of procyclical margin spirals.</t>
         </is>
       </c>
     </row>
@@ -47589,14 +47589,14 @@
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>**Highest-Risk Watch:**</t>
+          <t>**Highest-risk story to watch:**</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>Private credit's opaque expansion remains the most acute concern at level 8 (High), followed by Japan fiscal/JGB/carry trade, China's price spillover, Critical minerals as a weapon, AI build-out circular financing, AI power &amp; the grid bottleneck, Food &amp; fertilizer fragility, and Sea lanes &amp; undersea cables—all at level 7 (High).</t>
+          <t>Private credit's opaque expansion remains at High—the largest unmonitored leverage pool, most exposed to mark-to-market shocks and redemption pressure if rates or credit spreads spike.</t>
         </is>
       </c>
     </row>
